--- a/database/event/6348/event_6348_evp_summary.xlsx
+++ b/database/event/6348/event_6348_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.8852</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3563</v>
+        <v>2.2954</v>
       </c>
       <c r="E2" t="n">
         <v>6.8759</v>
@@ -548,7 +548,7 @@
         <v>1.47</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7446</v>
+        <v>1.6922</v>
       </c>
       <c r="E3" t="n">
         <v>5.3616</v>
@@ -594,7 +594,7 @@
         <v>1.3608</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5837</v>
+        <v>1.5335</v>
       </c>
       <c r="E4" t="n">
         <v>4.9633</v>
@@ -640,7 +640,7 @@
         <v>1.3464</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5624</v>
+        <v>1.5124</v>
       </c>
       <c r="E5" t="n">
         <v>4.9105</v>
@@ -686,7 +686,7 @@
         <v>1.1193</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2278</v>
+        <v>1.1825</v>
       </c>
       <c r="E6" t="n">
         <v>4.0823</v>
@@ -732,7 +732,7 @@
         <v>0.9933999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0423</v>
+        <v>0.9996</v>
       </c>
       <c r="E7" t="n">
         <v>3.6232</v>
@@ -778,7 +778,7 @@
         <v>0.9557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9867</v>
+        <v>0.9447</v>
       </c>
       <c r="E8" t="n">
         <v>3.4855</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1276</v>
+        <v>3.1161</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8575</v>
+        <v>0.8544</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8421</v>
+        <v>0.7975</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1276</v>
+        <v>3.1161</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0828</v>
+        <v>3.0713</v>
       </c>
       <c r="G9" t="n">
         <v>0.0448</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0828</v>
+        <v>3.0713</v>
       </c>
       <c r="I9" t="n">
         <v>3.0972</v>
@@ -870,7 +870,7 @@
         <v>0.8387</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8143</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>3.0588</v>
@@ -916,7 +916,7 @@
         <v>0.8264</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7963</v>
+        <v>0.7569</v>
       </c>
       <c r="E11" t="n">
         <v>3.0141</v>
@@ -962,7 +962,7 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.781</v>
+        <v>0.7418</v>
       </c>
       <c r="E12" t="n">
         <v>2.9762</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4283</v>
+        <v>2.4226</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5596</v>
+        <v>0.5213</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4283</v>
+        <v>2.4226</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5233</v>
+        <v>1.5176</v>
       </c>
       <c r="G13" t="n">
         <v>0.905</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5233</v>
+        <v>1.5176</v>
       </c>
       <c r="I13" t="n">
         <v>1.5304</v>
@@ -1054,7 +1054,7 @@
         <v>0.5047</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3222</v>
+        <v>0.2894</v>
       </c>
       <c r="E14" t="n">
         <v>1.8407</v>
@@ -1100,7 +1100,7 @@
         <v>0.4952</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3082</v>
+        <v>0.2756</v>
       </c>
       <c r="E15" t="n">
         <v>1.806</v>
@@ -1146,7 +1146,7 @@
         <v>0.4818</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2885</v>
+        <v>0.2561</v>
       </c>
       <c r="E16" t="n">
         <v>1.7571</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6851</v>
+        <v>1.6873</v>
       </c>
       <c r="C17" t="n">
-        <v>0.462</v>
+        <v>0.4626</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2594</v>
+        <v>0.2283</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6851</v>
+        <v>1.6873</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5806</v>
+        <v>-0.5784</v>
       </c>
       <c r="G17" t="n">
         <v>2.2657</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5806</v>
+        <v>-0.5784</v>
       </c>
       <c r="I17" t="n">
         <v>-0.5833</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6372</v>
+        <v>1.6358</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4489</v>
+        <v>0.4485</v>
       </c>
       <c r="D18" t="n">
-        <v>0.24</v>
+        <v>0.2078</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6372</v>
+        <v>1.6358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3832</v>
+        <v>0.3818</v>
       </c>
       <c r="G18" t="n">
         <v>1.254</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3832</v>
+        <v>0.3818</v>
       </c>
       <c r="I18" t="n">
         <v>0.385</v>
@@ -1284,7 +1284,7 @@
         <v>0.4305</v>
       </c>
       <c r="D19" t="n">
-        <v>0.213</v>
+        <v>0.1817</v>
       </c>
       <c r="E19" t="n">
         <v>1.5702</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3308</v>
+        <v>1.3299</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3649</v>
+        <v>0.3646</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1163</v>
+        <v>0.0859</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3308</v>
+        <v>1.3299</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2333</v>
+        <v>0.2324</v>
       </c>
       <c r="G20" t="n">
         <v>1.0975</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2333</v>
+        <v>0.2324</v>
       </c>
       <c r="I20" t="n">
         <v>0.2344</v>
@@ -1376,7 +1376,7 @@
         <v>0.3454</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="E21" t="n">
         <v>1.2597</v>
@@ -1422,7 +1422,7 @@
         <v>0.2541</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.047</v>
+        <v>-0.0747</v>
       </c>
       <c r="E22" t="n">
         <v>0.9267</v>
@@ -1468,7 +1468,7 @@
         <v>0.1601</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1854</v>
+        <v>-0.2112</v>
       </c>
       <c r="E23" t="n">
         <v>0.5841</v>
@@ -1514,7 +1514,7 @@
         <v>0.1492</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2015</v>
+        <v>-0.2271</v>
       </c>
       <c r="E24" t="n">
         <v>0.5443</v>
@@ -1560,7 +1560,7 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3225</v>
+        <v>-0.3465</v>
       </c>
       <c r="E25" t="n">
         <v>0.2446</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1764</v>
+        <v>-0.1774</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0484</v>
+        <v>-0.0486</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4926</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1764</v>
+        <v>-0.1774</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2754</v>
+        <v>0.2744</v>
       </c>
       <c r="G26" t="n">
         <v>-0.4518</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2754</v>
+        <v>0.2744</v>
       </c>
       <c r="I26" t="n">
         <v>0.2767</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0619</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5125</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2257</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1117</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5859</v>
+        <v>-0.6062</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4074</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1807</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6876</v>
+        <v>-0.7065</v>
       </c>
       <c r="E29" t="n">
         <v>-0.659</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.8007</v>
+        <v>-0.7951</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2195</v>
+        <v>-0.218</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7448</v>
+        <v>-0.7607</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.8007</v>
+        <v>-0.7951</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5198</v>
+        <v>-1.5142</v>
       </c>
       <c r="G30" t="n">
         <v>0.7191</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.5198</v>
+        <v>-1.5142</v>
       </c>
       <c r="I30" t="n">
         <v>-1.5269</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2196</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.745</v>
+        <v>-0.7631</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8011</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8682</v>
+        <v>-0.8712</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.238</v>
+        <v>-0.2389</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7721</v>
+        <v>-0.791</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8682</v>
+        <v>-0.8712</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8037</v>
+        <v>0.8007</v>
       </c>
       <c r="G32" t="n">
         <v>-1.6719</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8037</v>
+        <v>0.8007</v>
       </c>
       <c r="I32" t="n">
         <v>0.8074</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2587</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8025</v>
+        <v>-0.8198</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9435</v>
@@ -1974,7 +1974,7 @@
         <v>-0.297</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.859</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0832</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1858</v>
+        <v>-1.1807</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3251</v>
+        <v>-0.3237</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9004</v>
+        <v>-0.9143</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1858</v>
+        <v>-1.1807</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.372</v>
+        <v>-1.3669</v>
       </c>
       <c r="G35" t="n">
         <v>0.1862</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.372</v>
+        <v>-1.3669</v>
       </c>
       <c r="I35" t="n">
         <v>-1.3784</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2417</v>
+        <v>-1.2407</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3404</v>
+        <v>-0.3402</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.923</v>
+        <v>-0.9382</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2417</v>
+        <v>-1.2407</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2734</v>
+        <v>-0.2724</v>
       </c>
       <c r="G36" t="n">
         <v>-0.9683</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2734</v>
+        <v>-0.2724</v>
       </c>
       <c r="I36" t="n">
         <v>-0.2747</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3654</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9597</v>
+        <v>-0.9749</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3327</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4639</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1049</v>
+        <v>-1.118</v>
       </c>
       <c r="E38" t="n">
         <v>-1.692</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4662</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1082</v>
+        <v>-1.1213</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7002</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5058</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1666</v>
+        <v>-1.1789</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8448</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5206</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1884</v>
+        <v>-1.2004</v>
       </c>
       <c r="E41" t="n">
         <v>-1.8987</v>

--- a/database/event/6348/event_6348_evp_summary.xlsx
+++ b/database/event/6348/event_6348_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8759</v>
+        <v>5.9753</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8852</v>
+        <v>1.6383</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2954</v>
+        <v>2.0595</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8759</v>
+        <v>5.9753</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6754</v>
+        <v>3.3103</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2005</v>
+        <v>2.665</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6754</v>
+        <v>6.1771</v>
       </c>
       <c r="I2" t="n">
-        <v>2.979</v>
+        <v>3.2118</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2005</v>
+        <v>2.665</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>177</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1795</v>
+        <v>5.8768</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -538,47 +538,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3616</v>
+        <v>5.4762</v>
       </c>
       <c r="C3" t="n">
-        <v>1.47</v>
+        <v>1.5015</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6922</v>
+        <v>1.8342</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3616</v>
+        <v>5.4762</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8974</v>
+        <v>2.6106</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4642</v>
+        <v>2.8656</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8974</v>
+        <v>3.7117</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1589</v>
+        <v>1.9299</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4642</v>
+        <v>2.8656</v>
       </c>
       <c r="K3" t="n">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="L3" t="n">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6231</v>
+        <v>4.795500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>224</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9633</v>
+        <v>5.3505</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3608</v>
+        <v>1.467</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5335</v>
+        <v>1.7775</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9633</v>
+        <v>5.3505</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2384</v>
+        <v>2.2551</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7248</v>
+        <v>3.0954</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2384</v>
+        <v>2.2551</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2384</v>
+        <v>2.2551</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7248</v>
+        <v>3.0954</v>
       </c>
       <c r="K4" t="n">
         <v>122</v>
@@ -621,7 +621,7 @@
         <v>251</v>
       </c>
       <c r="M4" t="n">
-        <v>4.963200000000001</v>
+        <v>5.3505</v>
       </c>
       <c r="N4" t="n">
         <v>373</v>
@@ -630,311 +630,311 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9105</v>
+        <v>4.6175</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3464</v>
+        <v>1.266</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5124</v>
+        <v>1.4466</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9105</v>
+        <v>4.6175</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9792</v>
+        <v>3.3268</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9313</v>
+        <v>1.2907</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9792</v>
+        <v>6.2354</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6042</v>
+        <v>3.2421</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9313</v>
+        <v>1.2907</v>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="L5" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5355</v>
+        <v>4.5328</v>
       </c>
       <c r="N5" t="n">
-        <v>269</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0823</v>
+        <v>3.8062</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1193</v>
+        <v>1.0436</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1825</v>
+        <v>1.0803</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0823</v>
+        <v>3.8062</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0547</v>
+        <v>1.2433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0276</v>
+        <v>2.5629</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0547</v>
+        <v>1.2433</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2865</v>
+        <v>1.2433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0276</v>
+        <v>2.5629</v>
       </c>
       <c r="K6" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="L6" t="n">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3141</v>
+        <v>3.8062</v>
       </c>
       <c r="N6" t="n">
-        <v>269</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6232</v>
+        <v>3.7889</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9933999999999999</v>
+        <v>1.0388</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9996</v>
+        <v>1.0725</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6232</v>
+        <v>3.7889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8972</v>
+        <v>3.3581</v>
       </c>
       <c r="G7" t="n">
-        <v>2.726</v>
+        <v>0.4308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8972</v>
+        <v>6.3456</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8972</v>
+        <v>3.2994</v>
       </c>
       <c r="J7" t="n">
-        <v>2.726</v>
+        <v>0.4308</v>
       </c>
       <c r="K7" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="L7" t="n">
-        <v>251</v>
+        <v>177</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6232</v>
+        <v>3.7302</v>
       </c>
       <c r="N7" t="n">
-        <v>373</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4855</v>
+        <v>3.4132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9557</v>
+        <v>0.9358</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9447</v>
+        <v>0.9029</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4855</v>
+        <v>3.4132</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3423</v>
+        <v>1.9732</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1432</v>
+        <v>1.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3423</v>
+        <v>1.9732</v>
       </c>
       <c r="I8" t="n">
-        <v>2.709</v>
+        <v>1.9732</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1432</v>
+        <v>1.44</v>
       </c>
       <c r="K8" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8522</v>
+        <v>3.4132</v>
       </c>
       <c r="N8" t="n">
-        <v>269</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1161</v>
+        <v>3.3724</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8544</v>
+        <v>0.9246</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7975</v>
+        <v>0.8845</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1161</v>
+        <v>3.3724</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0713</v>
+        <v>2.2275</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0448</v>
+        <v>1.1449</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0713</v>
+        <v>2.2275</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0972</v>
+        <v>2.2275</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0448</v>
+        <v>1.1449</v>
       </c>
       <c r="K9" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L9" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>3.142</v>
+        <v>3.3724</v>
       </c>
       <c r="N9" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0588</v>
+        <v>3.2341</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8387</v>
+        <v>0.8867</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0588</v>
+        <v>3.2341</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8749</v>
+        <v>3.1056</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1839</v>
+        <v>0.1285</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8749</v>
+        <v>5.4559</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8749</v>
+        <v>2.8368</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1839</v>
+        <v>0.1285</v>
       </c>
       <c r="K10" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="L10" t="n">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0588</v>
+        <v>2.9653</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0141</v>
+        <v>3.1948</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8264</v>
+        <v>0.876</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7569</v>
+        <v>0.8043</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0141</v>
+        <v>3.1948</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7363</v>
+        <v>2.2313</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2778</v>
+        <v>0.9635</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7363</v>
+        <v>2.2313</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7363</v>
+        <v>2.2313</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2778</v>
+        <v>0.9635</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0141</v>
+        <v>3.1948</v>
       </c>
       <c r="N11" t="n">
         <v>180</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9762</v>
+        <v>3.147</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8628</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7418</v>
+        <v>0.7827</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9762</v>
+        <v>3.147</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5001</v>
+        <v>3.0448</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4761</v>
+        <v>0.1022</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5001</v>
+        <v>3.3262</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5001</v>
+        <v>3.463</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4761</v>
+        <v>0.1022</v>
       </c>
       <c r="K12" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="L12" t="n">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9762</v>
+        <v>3.5652</v>
       </c>
       <c r="N12" t="n">
-        <v>373</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4226</v>
+        <v>2.5479</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6642</v>
+        <v>0.6986</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5213</v>
+        <v>0.5122</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4226</v>
+        <v>2.5479</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5176</v>
+        <v>2.2142</v>
       </c>
       <c r="G13" t="n">
-        <v>0.905</v>
+        <v>0.3337</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5176</v>
+        <v>2.2142</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5304</v>
+        <v>2.2142</v>
       </c>
       <c r="J13" t="n">
-        <v>0.905</v>
+        <v>0.3337</v>
       </c>
       <c r="K13" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="L13" t="n">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4354</v>
+        <v>2.5479</v>
       </c>
       <c r="N13" t="n">
-        <v>318</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8407</v>
+        <v>2.4724</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5047</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2894</v>
+        <v>0.4782</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8407</v>
+        <v>2.4724</v>
       </c>
       <c r="F14" t="n">
-        <v>1.744</v>
+        <v>2.3512</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="H14" t="n">
-        <v>1.744</v>
+        <v>2.7979</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4136</v>
+        <v>1.4548</v>
       </c>
       <c r="J14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="K14" t="n">
         <v>137</v>
@@ -1081,7 +1081,7 @@
         <v>87</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5103</v>
+        <v>1.576</v>
       </c>
       <c r="N14" t="n">
         <v>224</v>
@@ -1090,507 +1090,507 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.806</v>
+        <v>2.1679</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4952</v>
+        <v>0.5944</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2756</v>
+        <v>0.3407</v>
       </c>
       <c r="E15" t="n">
-        <v>1.806</v>
+        <v>2.1679</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6125</v>
+        <v>1.4281</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8065</v>
+        <v>0.7398</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6125</v>
+        <v>1.4281</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1175</v>
+        <v>1.4868</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8065</v>
+        <v>0.7398</v>
       </c>
       <c r="K15" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L15" t="n">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="M15" t="n">
-        <v>1.311</v>
+        <v>2.2266</v>
       </c>
       <c r="N15" t="n">
-        <v>224</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7571</v>
+        <v>2.1187</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4818</v>
+        <v>0.5809</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2561</v>
+        <v>0.3185</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7571</v>
+        <v>2.1187</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1921</v>
+        <v>2.6066</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.4879</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1921</v>
+        <v>3.6976</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1921</v>
+        <v>1.9226</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.4879</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="L16" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7571</v>
+        <v>1.4347</v>
       </c>
       <c r="N16" t="n">
-        <v>180</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6873</v>
+        <v>2.0182</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4626</v>
+        <v>0.5534</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2283</v>
+        <v>0.2731</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6873</v>
+        <v>2.0182</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5784</v>
+        <v>1.4642</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2657</v>
+        <v>0.554</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5784</v>
+        <v>1.4642</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5833</v>
+        <v>1.4642</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2657</v>
+        <v>0.554</v>
       </c>
       <c r="K17" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
+        <v>74</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.0182</v>
+      </c>
+      <c r="N17" t="n">
         <v>180</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.6824</v>
-      </c>
-      <c r="N17" t="n">
-        <v>318</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6358</v>
+        <v>1.9334</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4485</v>
+        <v>0.5301</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2078</v>
+        <v>0.2348</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6358</v>
+        <v>1.9334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3818</v>
+        <v>0.6268</v>
       </c>
       <c r="G18" t="n">
-        <v>1.254</v>
+        <v>1.3066</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3818</v>
+        <v>0.6268</v>
       </c>
       <c r="I18" t="n">
-        <v>0.385</v>
+        <v>0.6268</v>
       </c>
       <c r="J18" t="n">
-        <v>1.254</v>
+        <v>1.3066</v>
       </c>
       <c r="K18" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="L18" t="n">
-        <v>93</v>
+        <v>251</v>
       </c>
       <c r="M18" t="n">
-        <v>1.639</v>
+        <v>1.9334</v>
       </c>
       <c r="N18" t="n">
-        <v>227</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5702</v>
+        <v>1.8761</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4305</v>
+        <v>0.5144</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1817</v>
+        <v>0.209</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5702</v>
+        <v>1.8761</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0106</v>
+        <v>2.1694</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5596</v>
+        <v>-0.2933</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0106</v>
+        <v>2.1694</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0106</v>
+        <v>1.128</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5596</v>
+        <v>-0.2933</v>
       </c>
       <c r="K19" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="L19" t="n">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5702</v>
+        <v>0.8346999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>373</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3299</v>
+        <v>1.7515</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3646</v>
+        <v>0.4802</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0859</v>
+        <v>0.1527</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3299</v>
+        <v>1.7515</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2324</v>
+        <v>0.5602</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0975</v>
+        <v>1.1913</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2324</v>
+        <v>0.5602</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2344</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0975</v>
+        <v>1.1913</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L20" t="n">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3319</v>
+        <v>1.7745</v>
       </c>
       <c r="N20" t="n">
-        <v>318</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2597</v>
+        <v>1.6975</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3454</v>
+        <v>0.4654</v>
       </c>
       <c r="D21" t="n">
-        <v>0.058</v>
+        <v>0.1283</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2597</v>
+        <v>1.6975</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3273</v>
+        <v>-0.2375</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.06759999999999999</v>
+        <v>1.935</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3273</v>
+        <v>-0.2375</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3273</v>
+        <v>-0.2473</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.06759999999999999</v>
+        <v>1.935</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>251</v>
+        <v>180</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2597</v>
+        <v>1.6877</v>
       </c>
       <c r="N21" t="n">
-        <v>373</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9267</v>
+        <v>1.2619</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2541</v>
+        <v>0.346</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0747</v>
+        <v>-0.0683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9267</v>
+        <v>1.2619</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9267</v>
+        <v>0.2784</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.9835</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9267</v>
+        <v>0.2784</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9267</v>
+        <v>0.2899</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.9835</v>
       </c>
       <c r="K22" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9267</v>
+        <v>1.2734</v>
       </c>
       <c r="N22" t="n">
-        <v>108</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5841</v>
+        <v>1.085</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1601</v>
+        <v>0.2975</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2112</v>
+        <v>-0.1482</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5841</v>
+        <v>1.085</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5841</v>
+        <v>2.4225</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1.3375</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5841</v>
+        <v>3.0491</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5841</v>
+        <v>1.5854</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1.3375</v>
       </c>
       <c r="K23" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5841</v>
+        <v>0.2479</v>
       </c>
       <c r="N23" t="n">
-        <v>108</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5443</v>
+        <v>1.0442</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1492</v>
+        <v>0.2863</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2271</v>
+        <v>-0.1666</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5443</v>
+        <v>1.0442</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0168</v>
+        <v>1.0442</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4725</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0168</v>
+        <v>1.0442</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8241000000000001</v>
+        <v>1.0442</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4725</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="L24" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3516000000000001</v>
+        <v>1.0442</v>
       </c>
       <c r="N24" t="n">
-        <v>224</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2446</v>
+        <v>0.6722</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.1843</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3465</v>
+        <v>-0.3345</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2446</v>
+        <v>0.6722</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9149</v>
+        <v>0.6722</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6703</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9149</v>
+        <v>0.6722</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5521</v>
+        <v>0.6722</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6703</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L25" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1181999999999999</v>
+        <v>0.6722</v>
       </c>
       <c r="N25" t="n">
-        <v>269</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1774</v>
+        <v>0.3123</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0486</v>
+        <v>0.0856</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.497</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1774</v>
+        <v>0.3123</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2744</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4518</v>
+        <v>-0.2457</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2744</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2767</v>
+        <v>0.5809</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4518</v>
+        <v>-0.2457</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>93</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1751</v>
+        <v>0.3351999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>227</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0619</v>
+        <v>0.0005</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.6371</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2257</v>
+        <v>0.002</v>
       </c>
       <c r="N27" t="n">
         <v>103</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1117</v>
+        <v>-0.0061</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6062</v>
+        <v>-0.6481</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4074</v>
+        <v>-0.0224</v>
       </c>
       <c r="N28" t="n">
         <v>103</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1807</v>
+        <v>-0.0455</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7065</v>
+        <v>-0.7129</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.659</v>
+        <v>-0.1659</v>
       </c>
       <c r="N29" t="n">
         <v>103</v>
@@ -1780,35 +1780,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7951</v>
+        <v>-0.208</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.218</v>
+        <v>-0.057</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7607</v>
+        <v>-0.7319</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7951</v>
+        <v>-0.208</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.5142</v>
+        <v>1.1291</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7191</v>
+        <v>-1.3371</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.5142</v>
+        <v>1.1291</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.5269</v>
+        <v>1.1755</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7191</v>
+        <v>-1.3371</v>
       </c>
       <c r="K30" t="n">
         <v>138</v>
@@ -1817,7 +1817,7 @@
         <v>180</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.8078</v>
+        <v>-0.1616</v>
       </c>
       <c r="N30" t="n">
         <v>318</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2196</v>
+        <v>-0.1345</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7631</v>
+        <v>-0.8595</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8011</v>
+        <v>-0.4905</v>
       </c>
       <c r="N31" t="n">
         <v>103</v>
@@ -1872,35 +1872,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8712</v>
+        <v>-0.622</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2389</v>
+        <v>-0.1705</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.791</v>
+        <v>-0.9188</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8712</v>
+        <v>-0.622</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8007</v>
+        <v>-1.1093</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.6719</v>
+        <v>0.4873</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8007</v>
+        <v>-1.1093</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8074</v>
+        <v>-1.1549</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.6719</v>
+        <v>0.4873</v>
       </c>
       <c r="K32" t="n">
         <v>138</v>
@@ -1909,7 +1909,7 @@
         <v>180</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8644999999999999</v>
+        <v>-0.6676</v>
       </c>
       <c r="N32" t="n">
         <v>318</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2587</v>
+        <v>-0.1808</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8198</v>
+        <v>-0.9358</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9435</v>
+        <v>-0.6596</v>
       </c>
       <c r="N33" t="n">
         <v>108</v>
@@ -1964,81 +1964,81 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0832</v>
+        <v>-0.7167</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.297</v>
+        <v>-0.1965</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.9616</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0832</v>
+        <v>-0.7167</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0832</v>
+        <v>-0.6224</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0832</v>
+        <v>-0.6224</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0832</v>
+        <v>-0.6224</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0832</v>
+        <v>-0.7166999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>103</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1807</v>
+        <v>-0.7168</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3237</v>
+        <v>-0.1965</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9143</v>
+        <v>-0.9616</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1807</v>
+        <v>-0.7168</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3669</v>
+        <v>-0.1183</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1862</v>
+        <v>-0.5985</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3669</v>
+        <v>-0.1183</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3784</v>
+        <v>-0.1232</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1862</v>
+        <v>-0.5985</v>
       </c>
       <c r="K35" t="n">
         <v>134</v>
@@ -2047,7 +2047,7 @@
         <v>93</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1922</v>
+        <v>-0.7217</v>
       </c>
       <c r="N35" t="n">
         <v>227</v>
@@ -2056,231 +2056,231 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2407</v>
+        <v>-0.7801</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3402</v>
+        <v>-0.2139</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9382</v>
+        <v>-0.9902</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2407</v>
+        <v>-0.7801</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2724</v>
+        <v>-0.7801</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9683</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2724</v>
+        <v>-0.7801</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2747</v>
+        <v>-0.7801</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9683</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L36" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.243</v>
+        <v>-0.7801</v>
       </c>
       <c r="N36" t="n">
-        <v>227</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3327</v>
+        <v>-0.8486</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3654</v>
+        <v>-0.2327</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9749</v>
+        <v>-1.0211</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3327</v>
+        <v>-0.8486</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9928</v>
+        <v>-1.0803</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3399</v>
+        <v>0.2317</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9928</v>
+        <v>-1.0803</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9928</v>
+        <v>-1.1247</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3399</v>
+        <v>0.2317</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="L37" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3327</v>
+        <v>-0.893</v>
       </c>
       <c r="N37" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F1KU</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.692</v>
+        <v>-1.1144</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4639</v>
+        <v>-0.3055</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.118</v>
+        <v>-1.1411</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.692</v>
+        <v>-1.1144</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.692</v>
+        <v>-0.6499</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4645</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.692</v>
+        <v>-0.6499</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.692</v>
+        <v>-0.3379</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4645</v>
       </c>
       <c r="K38" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.692</v>
+        <v>-0.8024</v>
       </c>
       <c r="N38" t="n">
-        <v>108</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7002</v>
+        <v>-1.3114</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4662</v>
+        <v>-0.3596</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1213</v>
+        <v>-1.23</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7002</v>
+        <v>-1.3114</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9254</v>
+        <v>-0.5075</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7748</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9254</v>
+        <v>-0.5075</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7501</v>
+        <v>-0.5075</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7748</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="L39" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5249</v>
+        <v>-1.3114</v>
       </c>
       <c r="N39" t="n">
-        <v>224</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>F1KU</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5058</v>
+        <v>-0.3692</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1789</v>
+        <v>-1.2459</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L40" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8448</v>
+        <v>-1.3466</v>
       </c>
       <c r="N40" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5206</v>
+        <v>-0.4326</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2004</v>
+        <v>-1.3504</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8987</v>
+        <v>-1.5779</v>
       </c>
       <c r="N41" t="n">
         <v>108</v>
@@ -2429,10 +2429,10 @@
         <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0329</v>
+        <v>1.0098</v>
       </c>
       <c r="J2" t="n">
-        <v>27.8883</v>
+        <v>27.2646</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6414</v>
+        <v>0.6248</v>
       </c>
       <c r="J3" t="n">
-        <v>17.3178</v>
+        <v>16.8696</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4808</v>
+        <v>0.4751</v>
       </c>
       <c r="J4" t="n">
-        <v>12.9816</v>
+        <v>12.8277</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3335</v>
+        <v>-0.2634</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.0045</v>
+        <v>-7.1118</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.92</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3945</v>
+        <v>-0.3252</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.6515</v>
+        <v>-8.7804</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6021</v>
+        <v>0.7271</v>
       </c>
       <c r="J7" t="n">
-        <v>16.2567</v>
+        <v>19.6317</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2834</v>
+        <v>0.3108</v>
       </c>
       <c r="J8" t="n">
-        <v>7.6518</v>
+        <v>8.3916</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2889</v>
+        <v>-0.1756</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.8003</v>
+        <v>-4.7412</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3046</v>
+        <v>-0.1861</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.2242</v>
+        <v>-5.0247</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4909</v>
+        <v>-0.3154</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.2543</v>
+        <v>-8.5158</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2716</v>
+        <v>0.2311</v>
       </c>
       <c r="J12" t="n">
-        <v>7.6048</v>
+        <v>6.4708</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2216</v>
+        <v>0.1856</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2048</v>
+        <v>5.1968</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1279</v>
+        <v>0.1043</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5812</v>
+        <v>2.9204</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.198</v>
+        <v>-0.1134</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.544</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2659</v>
+        <v>-0.1579</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.4452</v>
+        <v>-4.4212</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7275</v>
+        <v>0.6438</v>
       </c>
       <c r="J17" t="n">
-        <v>20.37</v>
+        <v>18.0264</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4292</v>
+        <v>0.3651</v>
       </c>
       <c r="J18" t="n">
-        <v>12.0176</v>
+        <v>10.2228</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1488</v>
+        <v>0.1475</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1664</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0921</v>
+        <v>0.103</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5788</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.66</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5881</v>
+        <v>-0.3853</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.4668</v>
+        <v>-10.7884</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8881</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>31.0835</v>
+        <v>30.4675</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8655</v>
+        <v>0.8469</v>
       </c>
       <c r="J23" t="n">
-        <v>30.2925</v>
+        <v>29.6415</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7964</v>
+        <v>0.7755</v>
       </c>
       <c r="J24" t="n">
-        <v>27.874</v>
+        <v>27.1425</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6318</v>
+        <v>-0.5737</v>
       </c>
       <c r="J25" t="n">
-        <v>-22.113</v>
+        <v>-20.0795</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6813</v>
+        <v>-0.6264</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.8455</v>
+        <v>-21.924</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4282</v>
+        <v>0.4954</v>
       </c>
       <c r="J27" t="n">
-        <v>14.987</v>
+        <v>17.339</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3416</v>
+        <v>0.3848</v>
       </c>
       <c r="J28" t="n">
-        <v>11.956</v>
+        <v>13.468</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3265</v>
+        <v>0.3658</v>
       </c>
       <c r="J29" t="n">
-        <v>11.4275</v>
+        <v>12.803</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.466</v>
+        <v>-0.2973</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.31</v>
+        <v>-10.4055</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5579</v>
+        <v>-0.3638</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.5265</v>
+        <v>-12.733</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.662</v>
+        <v>0.5027</v>
       </c>
       <c r="J32" t="n">
-        <v>17.874</v>
+        <v>13.5729</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.41</v>
       </c>
       <c r="I33" t="n">
-        <v>0.65</v>
+        <v>0.4953</v>
       </c>
       <c r="J33" t="n">
-        <v>17.55</v>
+        <v>13.3731</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2998</v>
+        <v>-0.1802</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.0946</v>
+        <v>-4.8654</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.389</v>
+        <v>-0.2418</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.503</v>
+        <v>-6.5286</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6127</v>
+        <v>-0.4042</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.5429</v>
+        <v>-10.9134</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7822</v>
+        <v>0.5478</v>
       </c>
       <c r="J37" t="n">
-        <v>21.1194</v>
+        <v>14.7906</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3071</v>
+        <v>0.2501</v>
       </c>
       <c r="J38" t="n">
-        <v>8.291700000000001</v>
+        <v>6.7527</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.13</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2594</v>
+        <v>0.2097</v>
       </c>
       <c r="J39" t="n">
-        <v>7.0038</v>
+        <v>5.6619</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3209</v>
+        <v>-0.1934</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.664300000000001</v>
+        <v>-5.2218</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.4611</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.576</v>
+        <v>-12.4497</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1496</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>41.3856</v>
+        <v>29.232</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2479</v>
+        <v>0.2214</v>
       </c>
       <c r="J43" t="n">
-        <v>8.9244</v>
+        <v>7.9704</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0335</v>
+        <v>-0.0051</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.206</v>
+        <v>-0.1836</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4961</v>
+        <v>-0.4419</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.8596</v>
+        <v>-15.9084</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.703</v>
+        <v>-0.6554</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.308</v>
+        <v>-23.5944</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2025</v>
+        <v>0.2213</v>
       </c>
       <c r="J47" t="n">
-        <v>7.29</v>
+        <v>7.9668</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1844</v>
+        <v>0.2006</v>
       </c>
       <c r="J48" t="n">
-        <v>6.6384</v>
+        <v>7.2216</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1657</v>
+        <v>0.1794</v>
       </c>
       <c r="J49" t="n">
-        <v>5.9652</v>
+        <v>6.4584</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1463</v>
+        <v>0.1578</v>
       </c>
       <c r="J50" t="n">
-        <v>5.2668</v>
+        <v>5.6808</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3881</v>
+        <v>-0.2413</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.9716</v>
+        <v>-8.6868</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2611</v>
+        <v>0.8992</v>
       </c>
       <c r="J52" t="n">
-        <v>30.2664</v>
+        <v>21.5808</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.859</v>
+        <v>0.6585</v>
       </c>
       <c r="J53" t="n">
-        <v>20.616</v>
+        <v>15.804</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4385</v>
+        <v>0.4438</v>
       </c>
       <c r="J54" t="n">
-        <v>10.524</v>
+        <v>10.6512</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4129</v>
+        <v>0.4291</v>
       </c>
       <c r="J55" t="n">
-        <v>9.909599999999999</v>
+        <v>10.2984</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.16</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3614</v>
+        <v>0.3992</v>
       </c>
       <c r="J56" t="n">
-        <v>8.6736</v>
+        <v>9.5808</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6615</v>
+        <v>0.62</v>
       </c>
       <c r="J57" t="n">
-        <v>15.876</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.065</v>
+        <v>-0.0747</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.56</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.65</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5392</v>
+        <v>-0.3572</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.9408</v>
+        <v>-8.572800000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6328</v>
+        <v>-0.4228</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.1872</v>
+        <v>-10.1472</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.47</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7704</v>
+        <v>-0.5245</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.4896</v>
+        <v>-12.588</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.43</v>
+        <v>0.4267</v>
       </c>
       <c r="J62" t="n">
-        <v>11.18</v>
+        <v>11.0942</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0352</v>
+        <v>-0.0419</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.9152</v>
+        <v>-1.0894</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3282</v>
+        <v>-0.208</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.533200000000001</v>
+        <v>-5.408</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.389</v>
+        <v>-0.248</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.114</v>
+        <v>-6.448</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4036</v>
+        <v>-0.2578</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.4936</v>
+        <v>-6.7028</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9457</v>
+        <v>0.6917</v>
       </c>
       <c r="J67" t="n">
-        <v>24.5882</v>
+        <v>17.9842</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.22</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6142</v>
+        <v>0.4988</v>
       </c>
       <c r="J68" t="n">
-        <v>15.9692</v>
+        <v>12.9688</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5605</v>
+        <v>0.4703</v>
       </c>
       <c r="J69" t="n">
-        <v>14.573</v>
+        <v>12.2278</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2233</v>
+        <v>0.2815</v>
       </c>
       <c r="J70" t="n">
-        <v>5.8058</v>
+        <v>7.319</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2494</v>
+        <v>-0.1738</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.4844</v>
+        <v>-4.5188</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.4789</v>
       </c>
       <c r="J72" t="n">
-        <v>23.7528</v>
+        <v>17.2404</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.612</v>
+        <v>0.4523</v>
       </c>
       <c r="J73" t="n">
-        <v>22.032</v>
+        <v>16.2828</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1384</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.9824</v>
+        <v>-2.3292</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.95</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1778</v>
+        <v>-0.091</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.4008</v>
+        <v>-3.276</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1778</v>
+        <v>-0.091</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.4008</v>
+        <v>-3.276</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7463</v>
+        <v>0.5557</v>
       </c>
       <c r="J77" t="n">
-        <v>26.8668</v>
+        <v>20.0052</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0232</v>
+        <v>0.0275</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1219</v>
+        <v>-0.065</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.3884</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.83</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3439</v>
+        <v>-0.2107</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.3804</v>
+        <v>-7.5852</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3877</v>
+        <v>-0.2411</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.9572</v>
+        <v>-8.679600000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3744</v>
+        <v>0.3851</v>
       </c>
       <c r="J82" t="n">
-        <v>9.359999999999999</v>
+        <v>9.6275</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1263</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.1575</v>
+        <v>-2.0775</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2251</v>
+        <v>-0.1391</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.6275</v>
+        <v>-3.4775</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2595</v>
+        <v>-0.1604</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.4875</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3082</v>
+        <v>-0.1918</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.705</v>
+        <v>-4.795</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8282</v>
+        <v>0.6166</v>
       </c>
       <c r="J87" t="n">
-        <v>20.705</v>
+        <v>15.415</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.22</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6352</v>
+        <v>0.5037</v>
       </c>
       <c r="J88" t="n">
-        <v>15.88</v>
+        <v>12.5925</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5567</v>
+        <v>0.4601</v>
       </c>
       <c r="J89" t="n">
-        <v>13.9175</v>
+        <v>11.5025</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.16</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4726</v>
+        <v>0.4159</v>
       </c>
       <c r="J90" t="n">
-        <v>11.815</v>
+        <v>10.3975</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6333</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.225</v>
+        <v>-15.8325</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.54</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2782</v>
+        <v>0.907</v>
       </c>
       <c r="J92" t="n">
-        <v>33.2332</v>
+        <v>23.582</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7867</v>
+        <v>0.611</v>
       </c>
       <c r="J93" t="n">
-        <v>20.4542</v>
+        <v>15.886</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.28</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7125</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>18.525</v>
+        <v>14.8486</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0964</v>
+        <v>0.1725</v>
       </c>
       <c r="J95" t="n">
-        <v>2.5064</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1406</v>
       </c>
       <c r="J96" t="n">
-        <v>1.6822</v>
+        <v>3.6556</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3608</v>
+        <v>0.3726</v>
       </c>
       <c r="J97" t="n">
-        <v>9.380800000000001</v>
+        <v>9.6876</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1141</v>
+        <v>-0.0911</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.9666</v>
+        <v>-2.3686</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1549</v>
+        <v>-0.1137</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.0274</v>
+        <v>-2.9562</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.222</v>
+        <v>-0.1452</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.772</v>
+        <v>-3.7752</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.62</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6042</v>
+        <v>-0.3994</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.7092</v>
+        <v>-10.3844</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3373</v>
+        <v>0.2872</v>
       </c>
       <c r="J102" t="n">
-        <v>13.8293</v>
+        <v>11.7752</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.109</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>4.469</v>
+        <v>3.1078</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.02</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0858</v>
+        <v>0.0557</v>
       </c>
       <c r="J104" t="n">
-        <v>3.5178</v>
+        <v>2.2837</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.492</v>
+        <v>-0.738</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6157</v>
+        <v>-0.407</v>
       </c>
       <c r="J106" t="n">
-        <v>-25.2437</v>
+        <v>-16.687</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.35</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5426</v>
+        <v>0.4136</v>
       </c>
       <c r="J107" t="n">
-        <v>22.2466</v>
+        <v>16.9576</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2575</v>
+        <v>0.2257</v>
       </c>
       <c r="J108" t="n">
-        <v>10.5575</v>
+        <v>9.2537</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1418</v>
+        <v>0.1459</v>
       </c>
       <c r="J109" t="n">
-        <v>5.8138</v>
+        <v>5.9819</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1052</v>
+        <v>0.1165</v>
       </c>
       <c r="J110" t="n">
-        <v>4.3132</v>
+        <v>4.7765</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0883</v>
+        <v>-0.0329</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.6203</v>
+        <v>-1.3489</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5516</v>
+        <v>1.0831</v>
       </c>
       <c r="J112" t="n">
-        <v>40.3416</v>
+        <v>28.1606</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0573</v>
+        <v>0.7568</v>
       </c>
       <c r="J113" t="n">
-        <v>27.4898</v>
+        <v>19.6768</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.299</v>
+        <v>-0.2296</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.774</v>
+        <v>-5.9696</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.82</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6028</v>
       </c>
       <c r="J115" t="n">
-        <v>-17.1548</v>
+        <v>-15.6728</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7563</v>
+        <v>-0.7066</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.6638</v>
+        <v>-18.3716</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.39</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6357</v>
+        <v>0.593</v>
       </c>
       <c r="J117" t="n">
-        <v>16.5282</v>
+        <v>15.418</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1951</v>
+        <v>0.2063</v>
       </c>
       <c r="J118" t="n">
-        <v>5.0726</v>
+        <v>5.3638</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2758</v>
+        <v>-0.1662</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.1708</v>
+        <v>-4.3212</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2758</v>
+        <v>-0.1662</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1708</v>
+        <v>-4.3212</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.76</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4387</v>
+        <v>-0.2779</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.4062</v>
+        <v>-7.2254</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.53</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2652</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>30.3648</v>
+        <v>21.5448</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7954</v>
+        <v>0.6129</v>
       </c>
       <c r="J123" t="n">
-        <v>19.0896</v>
+        <v>14.7096</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6439</v>
+        <v>0.5324</v>
       </c>
       <c r="J124" t="n">
-        <v>15.4536</v>
+        <v>12.7776</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6439</v>
+        <v>0.5324</v>
       </c>
       <c r="J125" t="n">
-        <v>15.4536</v>
+        <v>12.7776</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6661</v>
+        <v>-0.6047</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.9864</v>
+        <v>-14.5128</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>13.368</v>
+        <v>12.6888</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4482</v>
+        <v>0.4402</v>
       </c>
       <c r="J128" t="n">
-        <v>10.7568</v>
+        <v>10.5648</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2552</v>
+        <v>-0.1724</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.1248</v>
+        <v>-4.1376</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4613</v>
+        <v>-0.3</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.0712</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0386</v>
+        <v>-0.7376</v>
       </c>
       <c r="J131" t="n">
-        <v>-24.9264</v>
+        <v>-17.7024</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1466</v>
+        <v>0.0921</v>
       </c>
       <c r="J132" t="n">
-        <v>3.2252</v>
+        <v>2.0262</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.76</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.296</v>
+        <v>-0.2382</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.512</v>
+        <v>-5.2404</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.71</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3785</v>
+        <v>-0.2868</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.327</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.53</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6683</v>
+        <v>-0.4523</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.7026</v>
+        <v>-9.9506</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7977</v>
+        <v>-0.546</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.5494</v>
+        <v>-12.012</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7189</v>
+        <v>0.5204</v>
       </c>
       <c r="J137" t="n">
-        <v>15.8158</v>
+        <v>11.4488</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5506</v>
+        <v>0.4337</v>
       </c>
       <c r="J138" t="n">
-        <v>12.1132</v>
+        <v>9.541399999999999</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5375</v>
+        <v>0.4274</v>
       </c>
       <c r="J139" t="n">
-        <v>11.825</v>
+        <v>9.402799999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.306</v>
+        <v>0.315</v>
       </c>
       <c r="J140" t="n">
-        <v>6.732</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1639</v>
+        <v>0.19</v>
       </c>
       <c r="J141" t="n">
-        <v>3.6058</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9686</v>
+        <v>0.7055</v>
       </c>
       <c r="J142" t="n">
-        <v>27.1208</v>
+        <v>19.754</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6155</v>
+        <v>0.4991</v>
       </c>
       <c r="J143" t="n">
-        <v>17.234</v>
+        <v>13.9748</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3136</v>
+        <v>0.3524</v>
       </c>
       <c r="J144" t="n">
-        <v>8.780799999999999</v>
+        <v>9.8672</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.194</v>
+        <v>0.2529</v>
       </c>
       <c r="J145" t="n">
-        <v>5.432</v>
+        <v>7.0812</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0648</v>
+        <v>0.1277</v>
       </c>
       <c r="J146" t="n">
-        <v>1.8144</v>
+        <v>3.5756</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2696</v>
+        <v>0.2927</v>
       </c>
       <c r="J147" t="n">
-        <v>7.5488</v>
+        <v>8.195600000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1833</v>
+        <v>0.1888</v>
       </c>
       <c r="J148" t="n">
-        <v>5.1324</v>
+        <v>5.2864</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0168</v>
+        <v>0.0029</v>
       </c>
       <c r="J149" t="n">
-        <v>0.4704</v>
+        <v>0.08119999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1846</v>
+        <v>-0.1093</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.1688</v>
+        <v>-3.0604</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4071</v>
+        <v>-0.2563</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.3988</v>
+        <v>-7.1764</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3076</v>
+        <v>0.3438</v>
       </c>
       <c r="J152" t="n">
-        <v>9.228</v>
+        <v>10.314</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2433</v>
+        <v>0.2656</v>
       </c>
       <c r="J153" t="n">
-        <v>7.299</v>
+        <v>7.968</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.09</v>
       </c>
       <c r="I154" t="n">
-        <v>0.209</v>
+        <v>0.2249</v>
       </c>
       <c r="J154" t="n">
-        <v>6.27</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2119</v>
+        <v>-0.1235</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.357</v>
+        <v>-3.705</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4408</v>
+        <v>-0.279</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.224</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0942</v>
+        <v>1.0544</v>
       </c>
       <c r="J157" t="n">
-        <v>32.826</v>
+        <v>31.632</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5991</v>
       </c>
       <c r="J158" t="n">
-        <v>18.402</v>
+        <v>17.973</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3798</v>
+        <v>0.3979</v>
       </c>
       <c r="J159" t="n">
-        <v>11.394</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3031</v>
+        <v>-0.2323</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.093</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3351</v>
+        <v>-0.2645</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.053</v>
+        <v>-7.935</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4149</v>
+        <v>0.3479</v>
       </c>
       <c r="J162" t="n">
-        <v>11.6172</v>
+        <v>9.741199999999999</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4009</v>
+        <v>0.3354</v>
       </c>
       <c r="J163" t="n">
-        <v>11.2252</v>
+        <v>9.3912</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.18</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3281</v>
+        <v>0.2719</v>
       </c>
       <c r="J164" t="n">
-        <v>9.1868</v>
+        <v>7.6132</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2961</v>
+        <v>-0.1751</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.290800000000001</v>
+        <v>-4.9028</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.85</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3266</v>
+        <v>-0.1963</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.1448</v>
+        <v>-5.4964</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.3</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4633</v>
       </c>
       <c r="J167" t="n">
-        <v>14.2688</v>
+        <v>12.9724</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4564</v>
+        <v>0.4101</v>
       </c>
       <c r="J168" t="n">
-        <v>12.7792</v>
+        <v>11.4828</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0211</v>
+        <v>-0.0023</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.5908</v>
+        <v>-0.0644</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3172</v>
+        <v>-0.1916</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.881600000000001</v>
+        <v>-5.3648</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4599</v>
+        <v>-0.2919</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8772</v>
+        <v>-8.1732</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>0.828</v>
+        <v>1.035</v>
       </c>
       <c r="J172" t="n">
-        <v>19.044</v>
+        <v>23.805</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0989</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.2747</v>
+        <v>-2.1436</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5624</v>
+        <v>-0.3715</v>
       </c>
       <c r="J174" t="n">
-        <v>-12.9352</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.59</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6278</v>
+        <v>-0.4182</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.4394</v>
+        <v>-9.618600000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.74</v>
+        <v>-0.5013</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.02</v>
+        <v>-11.5299</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1908</v>
+        <v>1.1313</v>
       </c>
       <c r="J177" t="n">
-        <v>27.3884</v>
+        <v>26.0199</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.49</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1503</v>
+        <v>1.1065</v>
       </c>
       <c r="J178" t="n">
-        <v>26.4569</v>
+        <v>25.4495</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.41</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9816</v>
+        <v>0.9977</v>
       </c>
       <c r="J179" t="n">
-        <v>22.5768</v>
+        <v>22.9471</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5281</v>
+        <v>0.6128</v>
       </c>
       <c r="J180" t="n">
-        <v>12.1463</v>
+        <v>14.0944</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.531</v>
+        <v>-0.4571</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.213</v>
+        <v>-10.5133</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.68</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.3121</v>
+        <v>-0.2662</v>
       </c>
       <c r="J182" t="n">
-        <v>-6.242</v>
+        <v>-5.324</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.57</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4822</v>
+        <v>-0.382</v>
       </c>
       <c r="J183" t="n">
-        <v>-9.644</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.52</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.5675</v>
+        <v>-0.4296</v>
       </c>
       <c r="J184" t="n">
-        <v>-11.35</v>
+        <v>-8.592000000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5675</v>
+        <v>-0.4296</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.35</v>
+        <v>-8.592000000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-1.0094</v>
+        <v>-0.7099</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.188</v>
+        <v>-14.198</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.93</v>
       </c>
       <c r="I187" t="n">
-        <v>1.8811</v>
+        <v>1.5903</v>
       </c>
       <c r="J187" t="n">
-        <v>37.622</v>
+        <v>31.806</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.68</v>
       </c>
       <c r="I188" t="n">
-        <v>1.4432</v>
+        <v>1.3057</v>
       </c>
       <c r="J188" t="n">
-        <v>28.864</v>
+        <v>26.114</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.51</v>
       </c>
       <c r="I189" t="n">
-        <v>1.1029</v>
+        <v>1.1074</v>
       </c>
       <c r="J189" t="n">
-        <v>22.058</v>
+        <v>22.148</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2724</v>
+        <v>0.3768</v>
       </c>
       <c r="J190" t="n">
-        <v>5.448</v>
+        <v>7.536</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1704</v>
+        <v>0.2689</v>
       </c>
       <c r="J191" t="n">
-        <v>3.408</v>
+        <v>5.378</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3959</v>
+        <v>0.4551</v>
       </c>
       <c r="J192" t="n">
-        <v>11.877</v>
+        <v>13.653</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2591</v>
+        <v>0.285</v>
       </c>
       <c r="J193" t="n">
-        <v>7.773</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0645</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>1.935</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2631</v>
+        <v>-0.1568</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.893</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.385</v>
+        <v>-0.2397</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.55</v>
+        <v>-7.191</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.4</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0809</v>
+        <v>1.0417</v>
       </c>
       <c r="J197" t="n">
-        <v>32.427</v>
+        <v>31.251</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6718</v>
+        <v>0.6412</v>
       </c>
       <c r="J198" t="n">
-        <v>20.154</v>
+        <v>19.236</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1893</v>
+        <v>0.2129</v>
       </c>
       <c r="J199" t="n">
-        <v>5.679</v>
+        <v>6.387</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.516</v>
+        <v>-0.4556</v>
       </c>
       <c r="J200" t="n">
-        <v>-15.48</v>
+        <v>-13.668</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6204</v>
+        <v>-0.5643</v>
       </c>
       <c r="J201" t="n">
-        <v>-18.612</v>
+        <v>-16.929</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2942</v>
+        <v>1.1846</v>
       </c>
       <c r="J202" t="n">
-        <v>38.826</v>
+        <v>35.538</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0061</v>
+        <v>0.9892</v>
       </c>
       <c r="J203" t="n">
-        <v>30.183</v>
+        <v>29.676</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3049</v>
+        <v>0.3443</v>
       </c>
       <c r="J204" t="n">
-        <v>9.147</v>
+        <v>10.329</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3374</v>
+        <v>-0.2661</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.122</v>
+        <v>-7.983</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8753</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-26.259</v>
+        <v>-25.086</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3843</v>
+        <v>0.4393</v>
       </c>
       <c r="J207" t="n">
-        <v>11.529</v>
+        <v>13.179</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.02</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0692</v>
+        <v>0.0664</v>
       </c>
       <c r="J208" t="n">
-        <v>2.076</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.98</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0669</v>
+        <v>-0.0358</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.007</v>
+        <v>-1.074</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2099</v>
+        <v>-0.1228</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.297</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2607</v>
+        <v>-0.1559</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.821</v>
+        <v>-4.677</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.96</v>
       </c>
       <c r="I212" t="n">
-        <v>1.9329</v>
+        <v>1.6324</v>
       </c>
       <c r="J212" t="n">
-        <v>40.5909</v>
+        <v>34.2804</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.78</v>
       </c>
       <c r="I213" t="n">
-        <v>1.6406</v>
+        <v>1.4275</v>
       </c>
       <c r="J213" t="n">
-        <v>34.4526</v>
+        <v>29.9775</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.4</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8582</v>
+        <v>0.9615</v>
       </c>
       <c r="J214" t="n">
-        <v>18.0222</v>
+        <v>20.1915</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2315</v>
+        <v>0.3311</v>
       </c>
       <c r="J215" t="n">
-        <v>4.8615</v>
+        <v>6.9531</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4493</v>
+        <v>-0.3673</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.4353</v>
+        <v>-7.7133</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.95</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0482</v>
+        <v>-0.0005</v>
       </c>
       <c r="J217" t="n">
-        <v>1.0122</v>
+        <v>-0.0105</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2226</v>
+        <v>-0.1949</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.6746</v>
+        <v>-4.0929</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.65</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4485</v>
+        <v>-0.3349</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.4185</v>
+        <v>-7.0329</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.4</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.8244</v>
+        <v>-0.5666</v>
       </c>
       <c r="J220" t="n">
-        <v>-17.3124</v>
+        <v>-11.8986</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.4</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8244</v>
+        <v>-0.5666</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.3124</v>
+        <v>-11.8986</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4746</v>
+        <v>0.5582</v>
       </c>
       <c r="J222" t="n">
-        <v>19.4586</v>
+        <v>22.8862</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2379</v>
+        <v>0.2622</v>
       </c>
       <c r="J223" t="n">
-        <v>9.7539</v>
+        <v>10.7502</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0376</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.1488</v>
+        <v>-1.5416</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1002</v>
+        <v>-0.0517</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.1082</v>
+        <v>-2.1197</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.76</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4436</v>
+        <v>-0.2806</v>
       </c>
       <c r="J226" t="n">
-        <v>-18.1876</v>
+        <v>-11.5046</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7837</v>
+        <v>0.7509</v>
       </c>
       <c r="J227" t="n">
-        <v>32.1317</v>
+        <v>30.7869</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6117</v>
+        <v>0.5747</v>
       </c>
       <c r="J228" t="n">
-        <v>25.0797</v>
+        <v>23.5627</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.16</v>
       </c>
       <c r="I229" t="n">
-        <v>0.533</v>
+        <v>0.4965</v>
       </c>
       <c r="J229" t="n">
-        <v>21.853</v>
+        <v>20.3565</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5853</v>
+        <v>-0.5302</v>
       </c>
       <c r="J230" t="n">
-        <v>-23.9973</v>
+        <v>-21.7382</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6862</v>
+        <v>-0.6359</v>
       </c>
       <c r="J231" t="n">
-        <v>-28.1342</v>
+        <v>-26.0719</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2186</v>
+        <v>0.2114</v>
       </c>
       <c r="J232" t="n">
-        <v>5.6836</v>
+        <v>5.4964</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.98</v>
       </c>
       <c r="I233" t="n">
-        <v>0.0174</v>
+        <v>-0.0163</v>
       </c>
       <c r="J233" t="n">
-        <v>0.4524</v>
+        <v>-0.4238</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.83</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2797</v>
+        <v>-0.1903</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.2722</v>
+        <v>-4.9478</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4551</v>
+        <v>-0.2973</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.8326</v>
+        <v>-7.7298</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5918</v>
+        <v>-0.3919</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.3868</v>
+        <v>-10.1894</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5147</v>
+        <v>1.3376</v>
       </c>
       <c r="J237" t="n">
-        <v>39.3822</v>
+        <v>34.7776</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.42</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0002</v>
+        <v>1.0126</v>
       </c>
       <c r="J238" t="n">
-        <v>26.0052</v>
+        <v>26.3276</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5992</v>
+        <v>0.6818</v>
       </c>
       <c r="J239" t="n">
-        <v>15.5792</v>
+        <v>17.7268</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.2</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4507</v>
+        <v>0.539</v>
       </c>
       <c r="J240" t="n">
-        <v>11.7182</v>
+        <v>14.014</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1592</v>
+        <v>-0.0756</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.1392</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.99</v>
       </c>
       <c r="I242" t="n">
-        <v>2.0194</v>
+        <v>1.7324</v>
       </c>
       <c r="J242" t="n">
-        <v>52.5044</v>
+        <v>45.0424</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.17</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4159</v>
+        <v>0.4822</v>
       </c>
       <c r="J243" t="n">
-        <v>10.8134</v>
+        <v>12.5372</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.11</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2515</v>
+        <v>0.3239</v>
       </c>
       <c r="J244" t="n">
-        <v>6.539</v>
+        <v>8.4214</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3374</v>
+        <v>-0.2574</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.772399999999999</v>
+        <v>-6.6924</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4281</v>
+        <v>-0.3513</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.1306</v>
+        <v>-9.133800000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2398</v>
+        <v>-0.1857</v>
       </c>
       <c r="J247" t="n">
-        <v>-6.2348</v>
+        <v>-4.8282</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2757</v>
+        <v>-0.2056</v>
       </c>
       <c r="J248" t="n">
-        <v>-7.1682</v>
+        <v>-5.3456</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2757</v>
+        <v>-0.2056</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.1682</v>
+        <v>-5.3456</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3575</v>
+        <v>-0.2431</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.295</v>
+        <v>-6.3206</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3909</v>
+        <v>-0.2621</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1634</v>
+        <v>-6.8146</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.44</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1899</v>
+        <v>1.1125</v>
       </c>
       <c r="J252" t="n">
-        <v>35.697</v>
+        <v>33.375</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4057</v>
+        <v>0.3673</v>
       </c>
       <c r="J253" t="n">
-        <v>12.171</v>
+        <v>11.019</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2885</v>
+        <v>-0.2372</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.654999999999999</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4693</v>
+        <v>-0.4145</v>
       </c>
       <c r="J255" t="n">
-        <v>-14.079</v>
+        <v>-12.435</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.728</v>
+        <v>-0.6817</v>
       </c>
       <c r="J256" t="n">
-        <v>-21.84</v>
+        <v>-20.451</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.23</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4227</v>
+        <v>0.49</v>
       </c>
       <c r="J257" t="n">
-        <v>12.681</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J258" t="n">
-        <v>7.23</v>
+        <v>7.923</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1393</v>
+        <v>-0.0769</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.179</v>
+        <v>-2.307</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1393</v>
+        <v>-0.0769</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.179</v>
+        <v>-2.307</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3715</v>
+        <v>-0.2301</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.145</v>
+        <v>-6.903</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.9238</v>
+        <v>0.8986</v>
       </c>
       <c r="J262" t="n">
-        <v>27.714</v>
+        <v>26.958</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.09</v>
       </c>
       <c r="I263" t="n">
-        <v>0.333</v>
+        <v>0.3059</v>
       </c>
       <c r="J263" t="n">
-        <v>9.99</v>
+        <v>9.177</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.03</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1025</v>
+        <v>0.1217</v>
       </c>
       <c r="J264" t="n">
-        <v>3.075</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3602</v>
+        <v>-0.3031</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.806</v>
+        <v>-9.093</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.87</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5039</v>
+        <v>-0.4471</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.117</v>
+        <v>-13.413</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3359</v>
+        <v>0.374</v>
       </c>
       <c r="J267" t="n">
-        <v>10.077</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.98</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0417</v>
+        <v>-0.0339</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.251</v>
+        <v>-1.017</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0417</v>
+        <v>-0.0339</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.251</v>
+        <v>-1.017</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.842</v>
+        <v>-2.904</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.79</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3903</v>
+        <v>-0.2452</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.709</v>
+        <v>-7.356</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2292</v>
+        <v>1.145</v>
       </c>
       <c r="J272" t="n">
-        <v>28.2716</v>
+        <v>26.335</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.39</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0014</v>
+        <v>0.9919</v>
       </c>
       <c r="J273" t="n">
-        <v>23.0322</v>
+        <v>22.8137</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7765</v>
+        <v>0.7743</v>
       </c>
       <c r="J274" t="n">
-        <v>17.8595</v>
+        <v>17.8089</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.04</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0559</v>
+        <v>0.1227</v>
       </c>
       <c r="J275" t="n">
-        <v>1.2857</v>
+        <v>2.8221</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9308</v>
+        <v>-0.8971</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.4084</v>
+        <v>-20.6333</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.33</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5868</v>
+        <v>0.7052</v>
       </c>
       <c r="J277" t="n">
-        <v>13.4964</v>
+        <v>16.2196</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3534</v>
+        <v>0.3913</v>
       </c>
       <c r="J278" t="n">
-        <v>8.1282</v>
+        <v>8.9999</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.13</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3071</v>
+        <v>0.3318</v>
       </c>
       <c r="J279" t="n">
-        <v>7.0633</v>
+        <v>7.6314</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.54</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.7064</v>
+        <v>-0.4754</v>
       </c>
       <c r="J280" t="n">
-        <v>-16.2472</v>
+        <v>-10.9342</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.44</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8233</v>
+        <v>-0.5654</v>
       </c>
       <c r="J281" t="n">
-        <v>-18.9359</v>
+        <v>-13.0042</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.77</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0248</v>
+        <v>1.0021</v>
       </c>
       <c r="J282" t="n">
-        <v>29.7192</v>
+        <v>29.0609</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1386</v>
+        <v>0.145</v>
       </c>
       <c r="J283" t="n">
-        <v>4.0194</v>
+        <v>4.205</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.92</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2199</v>
+        <v>-0.122</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.3771</v>
+        <v>-3.538</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2368</v>
+        <v>-0.1335</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.8672</v>
+        <v>-3.8715</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4031</v>
+        <v>-0.2496</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.6899</v>
+        <v>-7.2384</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I287" t="n">
-        <v>0.536</v>
+        <v>0.4583</v>
       </c>
       <c r="J287" t="n">
-        <v>15.544</v>
+        <v>13.2907</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.11</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2164</v>
+        <v>0.1791</v>
       </c>
       <c r="J288" t="n">
-        <v>6.2756</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0242</v>
+        <v>0.0402</v>
       </c>
       <c r="J289" t="n">
-        <v>0.7018</v>
+        <v>1.1658</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.096</v>
+        <v>-0.0426</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.784</v>
+        <v>-1.2354</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2306</v>
+        <v>-0.1307</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.6874</v>
+        <v>-3.7903</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.55</v>
       </c>
       <c r="I292" t="n">
-        <v>1.248</v>
+        <v>1.1718</v>
       </c>
       <c r="J292" t="n">
-        <v>27.456</v>
+        <v>25.7796</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.085</v>
+        <v>1.0739</v>
       </c>
       <c r="J293" t="n">
-        <v>23.87</v>
+        <v>23.6258</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.42</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9769</v>
+        <v>1.0055</v>
       </c>
       <c r="J294" t="n">
-        <v>21.4918</v>
+        <v>22.121</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3592</v>
+        <v>0.4546</v>
       </c>
       <c r="J295" t="n">
-        <v>7.9024</v>
+        <v>10.0012</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.16</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3341</v>
+        <v>0.4289</v>
       </c>
       <c r="J296" t="n">
-        <v>7.3502</v>
+        <v>9.4358</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.95</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.008</v>
+        <v>-0.0392</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.176</v>
+        <v>-0.8624000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1344</v>
+        <v>-0.1249</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.9568</v>
+        <v>-2.7478</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2183</v>
+        <v>-0.1794</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.8026</v>
+        <v>-3.9468</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5252</v>
+        <v>-0.351</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.5544</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7748</v>
+        <v>-0.5281</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.0456</v>
+        <v>-11.6182</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.89</v>
       </c>
       <c r="I302" t="n">
-        <v>1.8043</v>
+        <v>1.5385</v>
       </c>
       <c r="J302" t="n">
-        <v>36.086</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.85</v>
       </c>
       <c r="I303" t="n">
-        <v>1.7353</v>
+        <v>1.4936</v>
       </c>
       <c r="J303" t="n">
-        <v>34.706</v>
+        <v>29.872</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7814</v>
+        <v>0.9107</v>
       </c>
       <c r="J304" t="n">
-        <v>15.628</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.25</v>
       </c>
       <c r="I305" t="n">
-        <v>0.498</v>
+        <v>0.6182</v>
       </c>
       <c r="J305" t="n">
-        <v>9.960000000000001</v>
+        <v>12.364</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3365</v>
+        <v>0.4472</v>
       </c>
       <c r="J306" t="n">
-        <v>6.73</v>
+        <v>8.944000000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.77</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2085</v>
+        <v>-0.1888</v>
       </c>
       <c r="J307" t="n">
-        <v>-4.17</v>
+        <v>-3.776</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.76</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.224</v>
+        <v>-0.2001</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.48</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.5468</v>
+        <v>-0.403</v>
       </c>
       <c r="J309" t="n">
-        <v>-10.936</v>
+        <v>-8.06</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.7032</v>
+        <v>-0.4848</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.064</v>
+        <v>-9.696</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.23</v>
       </c>
       <c r="I311" t="n">
-        <v>-1.019</v>
+        <v>-0.7181</v>
       </c>
       <c r="J311" t="n">
-        <v>-20.38</v>
+        <v>-14.362</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.64</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4082</v>
+        <v>1.2746</v>
       </c>
       <c r="J312" t="n">
-        <v>26.7558</v>
+        <v>24.2174</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.59</v>
       </c>
       <c r="I313" t="n">
-        <v>1.3125</v>
+        <v>1.2149</v>
       </c>
       <c r="J313" t="n">
-        <v>24.9375</v>
+        <v>23.0831</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.52</v>
       </c>
       <c r="I314" t="n">
-        <v>1.1734</v>
+        <v>1.1306</v>
       </c>
       <c r="J314" t="n">
-        <v>22.2946</v>
+        <v>21.4814</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3978</v>
+        <v>0.4986</v>
       </c>
       <c r="J315" t="n">
-        <v>7.5582</v>
+        <v>9.4734</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.98</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2761</v>
+        <v>-0.1875</v>
       </c>
       <c r="J316" t="n">
-        <v>-5.2459</v>
+        <v>-3.5625</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.08</v>
       </c>
       <c r="I317" t="n">
-        <v>0.282</v>
+        <v>0.2903</v>
       </c>
       <c r="J317" t="n">
-        <v>5.358</v>
+        <v>5.5157</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.92</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0743</v>
+        <v>-0.0828</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.4117</v>
+        <v>-1.5732</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.76</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3636</v>
+        <v>-0.2505</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.9084</v>
+        <v>-4.7595</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.61</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5878</v>
+        <v>-0.3918</v>
       </c>
       <c r="J320" t="n">
-        <v>-11.1682</v>
+        <v>-7.4442</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.51</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7174</v>
+        <v>-0.4849</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.6306</v>
+        <v>-9.213100000000001</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.59</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3454</v>
+        <v>1.2286</v>
       </c>
       <c r="J322" t="n">
-        <v>29.5988</v>
+        <v>27.0292</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.55</v>
       </c>
       <c r="I323" t="n">
-        <v>1.2676</v>
+        <v>1.1796</v>
       </c>
       <c r="J323" t="n">
-        <v>27.8872</v>
+        <v>25.9512</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.23</v>
       </c>
       <c r="I324" t="n">
-        <v>0.525</v>
+        <v>0.6115</v>
       </c>
       <c r="J324" t="n">
-        <v>11.55</v>
+        <v>13.453</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.298</v>
+        <v>0.3859</v>
       </c>
       <c r="J325" t="n">
-        <v>6.556</v>
+        <v>8.489800000000001</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.05</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0433</v>
+        <v>0.1255</v>
       </c>
       <c r="J326" t="n">
-        <v>0.9526</v>
+        <v>2.761</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5445</v>
+        <v>0.6534</v>
       </c>
       <c r="J327" t="n">
-        <v>11.979</v>
+        <v>14.3748</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.1899</v>
+        <v>-0.16</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.1778</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.83</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2234</v>
+        <v>-0.1812</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.9148</v>
+        <v>-3.9864</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.58</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.4181</v>
       </c>
       <c r="J330" t="n">
-        <v>-13.739</v>
+        <v>-9.1982</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.31</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.9529</v>
+        <v>-0.6669</v>
       </c>
       <c r="J331" t="n">
-        <v>-20.9638</v>
+        <v>-14.6718</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6348/event_6348_evp_summary.xlsx
+++ b/database/event/6348/event_6348_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9753</v>
+        <v>6.0907</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6383</v>
+        <v>1.6699</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0595</v>
+        <v>2.1484</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9753</v>
+        <v>6.0907</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3103</v>
+        <v>3.2529</v>
       </c>
       <c r="G2" t="n">
-        <v>2.665</v>
+        <v>2.8378</v>
       </c>
       <c r="H2" t="n">
-        <v>6.1771</v>
+        <v>5.8384</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2118</v>
+        <v>3.1527</v>
       </c>
       <c r="J2" t="n">
-        <v>2.665</v>
+        <v>2.8378</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>177</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8768</v>
+        <v>5.9905</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4762</v>
+        <v>5.4856</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5015</v>
+        <v>1.504</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8342</v>
+        <v>1.873</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4762</v>
+        <v>5.4856</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6106</v>
+        <v>2.5537</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8656</v>
+        <v>2.9319</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7117</v>
+        <v>3.5315</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9299</v>
+        <v>1.907</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8656</v>
+        <v>2.9319</v>
       </c>
       <c r="K3" t="n">
         <v>92</v>
@@ -575,7 +575,7 @@
         <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>4.795500000000001</v>
+        <v>4.838900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>269</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3505</v>
+        <v>5.4455</v>
       </c>
       <c r="C4" t="n">
-        <v>1.467</v>
+        <v>1.493</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7775</v>
+        <v>1.8547</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3505</v>
+        <v>5.4455</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2551</v>
+        <v>2.1312</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0954</v>
+        <v>3.3143</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2551</v>
+        <v>2.1312</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2551</v>
+        <v>2.1312</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0954</v>
+        <v>3.3143</v>
       </c>
       <c r="K4" t="n">
         <v>122</v>
@@ -621,7 +621,7 @@
         <v>251</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3505</v>
+        <v>5.4455</v>
       </c>
       <c r="N4" t="n">
         <v>373</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6175</v>
+        <v>4.6733</v>
       </c>
       <c r="C5" t="n">
-        <v>1.266</v>
+        <v>1.2813</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4466</v>
+        <v>1.5032</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6175</v>
+        <v>4.6733</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3268</v>
+        <v>3.2497</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2907</v>
+        <v>1.4236</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2354</v>
+        <v>5.8277</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2421</v>
+        <v>3.1469</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2907</v>
+        <v>1.4236</v>
       </c>
       <c r="K5" t="n">
         <v>137</v>
@@ -667,7 +667,7 @@
         <v>87</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5328</v>
+        <v>4.5705</v>
       </c>
       <c r="N5" t="n">
         <v>224</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8062</v>
+        <v>3.8446</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0436</v>
+        <v>1.0541</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0803</v>
+        <v>1.1259</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8062</v>
+        <v>3.8446</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2433</v>
+        <v>1.234</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5629</v>
+        <v>2.6106</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2433</v>
+        <v>1.234</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2433</v>
+        <v>1.234</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5629</v>
+        <v>2.6106</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -713,7 +713,7 @@
         <v>251</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8062</v>
+        <v>3.8446</v>
       </c>
       <c r="N6" t="n">
         <v>373</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7889</v>
+        <v>3.8095</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0388</v>
+        <v>1.0445</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0725</v>
+        <v>1.11</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7889</v>
+        <v>3.8095</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3581</v>
+        <v>3.3469</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4308</v>
+        <v>0.4626</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3456</v>
+        <v>6.1486</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2994</v>
+        <v>3.3202</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4308</v>
+        <v>0.4626</v>
       </c>
       <c r="K7" t="n">
         <v>92</v>
@@ -759,7 +759,7 @@
         <v>177</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7302</v>
+        <v>3.7828</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4132</v>
+        <v>3.5166</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9358</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9029</v>
+        <v>0.9766</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4132</v>
+        <v>3.5166</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9732</v>
+        <v>1.8643</v>
       </c>
       <c r="G8" t="n">
-        <v>1.44</v>
+        <v>1.6523</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9732</v>
+        <v>1.8643</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9732</v>
+        <v>1.8643</v>
       </c>
       <c r="J8" t="n">
-        <v>1.44</v>
+        <v>1.6523</v>
       </c>
       <c r="K8" t="n">
         <v>122</v>
@@ -805,7 +805,7 @@
         <v>251</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4132</v>
+        <v>3.5166</v>
       </c>
       <c r="N8" t="n">
         <v>373</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3724</v>
+        <v>3.3886</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9246</v>
+        <v>0.9291</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8845</v>
+        <v>0.9184</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3724</v>
+        <v>3.3886</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2275</v>
+        <v>2.1253</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1449</v>
+        <v>1.2633</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2275</v>
+        <v>2.1253</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2275</v>
+        <v>2.1253</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1449</v>
+        <v>1.2633</v>
       </c>
       <c r="K9" t="n">
         <v>106</v>
@@ -851,7 +851,7 @@
         <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3724</v>
+        <v>3.3886</v>
       </c>
       <c r="N9" t="n">
         <v>180</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2341</v>
+        <v>3.3258</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8867</v>
+        <v>0.9119</v>
       </c>
       <c r="D10" t="n">
-        <v>0.822</v>
+        <v>0.8898</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2341</v>
+        <v>3.3258</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1056</v>
+        <v>3.0372</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1285</v>
+        <v>0.2886</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4559</v>
+        <v>5.1266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8368</v>
+        <v>2.7683</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1285</v>
+        <v>0.2886</v>
       </c>
       <c r="K10" t="n">
         <v>92</v>
@@ -897,7 +897,7 @@
         <v>177</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9653</v>
+        <v>3.0569</v>
       </c>
       <c r="N10" t="n">
         <v>269</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1948</v>
+        <v>3.2376</v>
       </c>
       <c r="C11" t="n">
-        <v>0.876</v>
+        <v>0.8877</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8043</v>
+        <v>0.8496</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1948</v>
+        <v>3.2376</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2313</v>
+        <v>2.1587</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9635</v>
+        <v>1.0789</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2313</v>
+        <v>2.1587</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2313</v>
+        <v>2.1587</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9635</v>
+        <v>1.0789</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1948</v>
+        <v>3.2376</v>
       </c>
       <c r="N11" t="n">
         <v>180</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.147</v>
+        <v>2.8422</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8628</v>
+        <v>0.7793</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7827</v>
+        <v>0.6696</v>
       </c>
       <c r="E12" t="n">
-        <v>3.147</v>
+        <v>2.8422</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0448</v>
+        <v>2.7156</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1022</v>
+        <v>0.1266</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3262</v>
+        <v>3.2186</v>
       </c>
       <c r="I12" t="n">
-        <v>3.463</v>
+        <v>3.3015</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1022</v>
+        <v>0.1266</v>
       </c>
       <c r="K12" t="n">
         <v>134</v>
@@ -989,7 +989,7 @@
         <v>93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5652</v>
+        <v>3.4281</v>
       </c>
       <c r="N12" t="n">
         <v>227</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5479</v>
+        <v>2.552</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6986</v>
+        <v>0.6997</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5122</v>
+        <v>0.5375</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5479</v>
+        <v>2.552</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2142</v>
+        <v>2.1346</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3337</v>
+        <v>0.4174</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2142</v>
+        <v>2.1346</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2142</v>
+        <v>2.1346</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3337</v>
+        <v>0.4174</v>
       </c>
       <c r="K13" t="n">
         <v>122</v>
@@ -1035,7 +1035,7 @@
         <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5479</v>
+        <v>2.552</v>
       </c>
       <c r="N13" t="n">
         <v>373</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4724</v>
+        <v>2.4527</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6725</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4782</v>
+        <v>0.4923</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4724</v>
+        <v>2.4527</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3512</v>
+        <v>2.2979</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1212</v>
+        <v>0.1548</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7979</v>
+        <v>2.6874</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4548</v>
+        <v>1.4512</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1212</v>
+        <v>0.1548</v>
       </c>
       <c r="K14" t="n">
         <v>137</v>
@@ -1081,7 +1081,7 @@
         <v>87</v>
       </c>
       <c r="M14" t="n">
-        <v>1.576</v>
+        <v>1.606</v>
       </c>
       <c r="N14" t="n">
         <v>224</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1679</v>
+        <v>2.2176</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5944</v>
+        <v>0.608</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3407</v>
+        <v>0.3853</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1679</v>
+        <v>2.2176</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4281</v>
+        <v>1.3608</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7398</v>
+        <v>0.8568</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4281</v>
+        <v>1.3608</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4868</v>
+        <v>1.3959</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7398</v>
+        <v>0.8568</v>
       </c>
       <c r="K15" t="n">
         <v>138</v>
@@ -1127,7 +1127,7 @@
         <v>180</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2266</v>
+        <v>2.2527</v>
       </c>
       <c r="N15" t="n">
         <v>318</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1187</v>
+        <v>2.1001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5809</v>
+        <v>0.5758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3185</v>
+        <v>0.3318</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1187</v>
+        <v>2.1001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6066</v>
+        <v>0.6193</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4879</v>
+        <v>1.4808</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6976</v>
+        <v>0.6193</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9226</v>
+        <v>0.6193</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4879</v>
+        <v>1.4808</v>
       </c>
       <c r="K16" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="L16" t="n">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4347</v>
+        <v>2.1001</v>
       </c>
       <c r="N16" t="n">
-        <v>224</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0182</v>
+        <v>2.0449</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5534</v>
+        <v>0.5607</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2731</v>
+        <v>0.3067</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0182</v>
+        <v>2.0449</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4642</v>
+        <v>1.4433</v>
       </c>
       <c r="G17" t="n">
-        <v>0.554</v>
+        <v>0.6016</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4642</v>
+        <v>1.4433</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4642</v>
+        <v>1.4433</v>
       </c>
       <c r="J17" t="n">
-        <v>0.554</v>
+        <v>0.6016</v>
       </c>
       <c r="K17" t="n">
         <v>106</v>
@@ -1219,7 +1219,7 @@
         <v>74</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0182</v>
+        <v>2.0449</v>
       </c>
       <c r="N17" t="n">
         <v>180</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9334</v>
+        <v>2.0441</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5301</v>
+        <v>0.5605</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2348</v>
+        <v>0.3063</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9334</v>
+        <v>2.0441</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6268</v>
+        <v>2.5685</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3066</v>
+        <v>-0.5244</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6268</v>
+        <v>3.5802</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6268</v>
+        <v>1.9333</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3066</v>
+        <v>-0.5244</v>
       </c>
       <c r="K18" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="L18" t="n">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9334</v>
+        <v>1.4089</v>
       </c>
       <c r="N18" t="n">
-        <v>373</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8761</v>
+        <v>1.8844</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5144</v>
+        <v>0.5167</v>
       </c>
       <c r="D19" t="n">
-        <v>0.209</v>
+        <v>0.2336</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8761</v>
+        <v>1.8844</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1694</v>
+        <v>0.5921</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2933</v>
+        <v>1.2923</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1694</v>
+        <v>0.5921</v>
       </c>
       <c r="I19" t="n">
-        <v>1.128</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2933</v>
+        <v>1.2923</v>
       </c>
       <c r="K19" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8346999999999999</v>
+        <v>1.8997</v>
       </c>
       <c r="N19" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7515</v>
+        <v>1.8677</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4802</v>
+        <v>0.5121</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1527</v>
+        <v>0.226</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7515</v>
+        <v>1.8677</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5602</v>
+        <v>-0.2783</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1913</v>
+        <v>2.146</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5602</v>
+        <v>-0.2783</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5832000000000001</v>
+        <v>-0.2855</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1913</v>
+        <v>2.146</v>
       </c>
       <c r="K20" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7745</v>
+        <v>1.8605</v>
       </c>
       <c r="N20" t="n">
-        <v>227</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6975</v>
+        <v>1.6474</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4654</v>
+        <v>0.4517</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1283</v>
+        <v>0.1257</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6975</v>
+        <v>1.6474</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2375</v>
+        <v>1.9724</v>
       </c>
       <c r="G21" t="n">
-        <v>1.935</v>
+        <v>-0.325</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2375</v>
+        <v>1.9724</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2473</v>
+        <v>1.0651</v>
       </c>
       <c r="J21" t="n">
-        <v>1.935</v>
+        <v>-0.325</v>
       </c>
       <c r="K21" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L21" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6877</v>
+        <v>0.7401</v>
       </c>
       <c r="N21" t="n">
-        <v>318</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2619</v>
+        <v>1.3262</v>
       </c>
       <c r="C22" t="n">
-        <v>0.346</v>
+        <v>0.3636</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0683</v>
+        <v>-0.0205</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2619</v>
+        <v>1.3262</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2784</v>
+        <v>0.2307</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9835</v>
+        <v>1.0955</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2784</v>
+        <v>0.2307</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2899</v>
+        <v>0.2366</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9835</v>
+        <v>1.0955</v>
       </c>
       <c r="K22" t="n">
         <v>138</v>
@@ -1449,7 +1449,7 @@
         <v>180</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2734</v>
+        <v>1.3321</v>
       </c>
       <c r="N22" t="n">
         <v>318</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.085</v>
+        <v>1.0655</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2975</v>
+        <v>0.2921</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1482</v>
+        <v>-0.1392</v>
       </c>
       <c r="E23" t="n">
-        <v>1.085</v>
+        <v>1.0655</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4225</v>
+        <v>2.3776</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3375</v>
+        <v>-1.3121</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0491</v>
+        <v>2.9502</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5854</v>
+        <v>1.5931</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3375</v>
+        <v>-1.3121</v>
       </c>
       <c r="K23" t="n">
         <v>92</v>
@@ -1495,7 +1495,7 @@
         <v>177</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2479</v>
+        <v>0.2809999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>269</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2863</v>
+        <v>0.2694</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1666</v>
+        <v>-0.1769</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0442</v>
+        <v>0.9826</v>
       </c>
       <c r="N24" t="n">
         <v>108</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1843</v>
+        <v>0.1679</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3345</v>
+        <v>-0.3455</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6722</v>
+        <v>0.6122</v>
       </c>
       <c r="N25" t="n">
         <v>108</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3123</v>
+        <v>0.2646</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0856</v>
+        <v>0.0725</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.497</v>
+        <v>-0.5038</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3123</v>
+        <v>0.2646</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2457</v>
+        <v>-0.2574</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5809</v>
+        <v>0.5355</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2457</v>
+        <v>-0.2574</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>93</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3351999999999999</v>
+        <v>0.2781</v>
       </c>
       <c r="N26" t="n">
         <v>227</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0005</v>
+        <v>-0.0157</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6371</v>
+        <v>-0.6503</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="F27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="I27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.002</v>
+        <v>-0.0574</v>
       </c>
       <c r="N27" t="n">
         <v>103</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0061</v>
+        <v>-0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6481</v>
+        <v>-0.6573</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0224</v>
+        <v>-0.0728</v>
       </c>
       <c r="N28" t="n">
         <v>103</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0455</v>
+        <v>-0.0539</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7129</v>
+        <v>-0.7137</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1659</v>
+        <v>-0.1965</v>
       </c>
       <c r="N29" t="n">
         <v>103</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.208</v>
+        <v>-0.2158</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.057</v>
+        <v>-0.0592</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7319</v>
+        <v>-0.7224</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.208</v>
+        <v>-0.2158</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1291</v>
+        <v>1.0614</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.3371</v>
+        <v>-1.2772</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1291</v>
+        <v>1.0614</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1755</v>
+        <v>1.0887</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.3371</v>
+        <v>-1.2772</v>
       </c>
       <c r="K30" t="n">
         <v>138</v>
@@ -1817,7 +1817,7 @@
         <v>180</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1616</v>
+        <v>-0.1884999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>318</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4905</v>
+        <v>-0.4608</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1345</v>
+        <v>-0.1263</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8595</v>
+        <v>-0.834</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4905</v>
+        <v>-0.4608</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4905</v>
+        <v>-1.0992</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.6384</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4905</v>
+        <v>-1.0992</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4905</v>
+        <v>-1.1275</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.6384</v>
       </c>
       <c r="K31" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4905</v>
+        <v>-0.4891</v>
       </c>
       <c r="N31" t="n">
-        <v>103</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.622</v>
+        <v>-0.5305</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1705</v>
+        <v>-0.1455</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9188</v>
+        <v>-0.8657</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.622</v>
+        <v>-0.5305</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1093</v>
+        <v>-0.5305</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4873</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1093</v>
+        <v>-0.5305</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1549</v>
+        <v>-0.5305</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4873</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="L32" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6676</v>
+        <v>-0.5305</v>
       </c>
       <c r="N32" t="n">
-        <v>318</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6596</v>
+        <v>-0.7114</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1808</v>
+        <v>-0.1951</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9358</v>
+        <v>-0.948</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6596</v>
+        <v>-0.7114</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6596</v>
+        <v>-0.6095</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.1019</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6596</v>
+        <v>-0.6095</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6596</v>
+        <v>-0.6095</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.1019</v>
       </c>
       <c r="K33" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6596</v>
+        <v>-0.7114</v>
       </c>
       <c r="N33" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7167</v>
+        <v>-0.7228</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1965</v>
+        <v>-0.1982</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9616</v>
+        <v>-0.9532</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7167</v>
+        <v>-0.7228</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6224</v>
+        <v>-0.7228</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6224</v>
+        <v>-0.7228</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6224</v>
+        <v>-0.7228</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7166999999999999</v>
+        <v>-0.7228</v>
       </c>
       <c r="N34" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7168</v>
+        <v>-0.7944</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1965</v>
+        <v>-0.2178</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9616</v>
+        <v>-0.9858</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7168</v>
+        <v>-0.7944</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1183</v>
+        <v>-0.1694</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5985</v>
+        <v>-0.625</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1183</v>
+        <v>-0.1694</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1232</v>
+        <v>-0.1738</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5985</v>
+        <v>-0.625</v>
       </c>
       <c r="K35" t="n">
         <v>134</v>
@@ -2047,7 +2047,7 @@
         <v>93</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7217</v>
+        <v>-0.7988</v>
       </c>
       <c r="N35" t="n">
         <v>227</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7801</v>
+        <v>-0.8015</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2139</v>
+        <v>-0.2198</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9902</v>
+        <v>-0.9891</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7801</v>
+        <v>-0.8015</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7801</v>
+        <v>-1.042</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.2405</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7801</v>
+        <v>-1.042</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7801</v>
+        <v>-1.0689</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.2405</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7801</v>
+        <v>-0.8284</v>
       </c>
       <c r="N36" t="n">
-        <v>103</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8486</v>
+        <v>-0.8081</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2327</v>
+        <v>-0.2216</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0211</v>
+        <v>-0.9921</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8486</v>
+        <v>-0.8081</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0803</v>
+        <v>-0.8081</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2317</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0803</v>
+        <v>-0.8081</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1247</v>
+        <v>-0.8081</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2317</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.893</v>
+        <v>-0.8081</v>
       </c>
       <c r="N37" t="n">
-        <v>227</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1144</v>
+        <v>-1.132</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3055</v>
+        <v>-0.3104</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1411</v>
+        <v>-1.1395</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1144</v>
+        <v>-1.132</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6499</v>
+        <v>-0.6317</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4645</v>
+        <v>-0.5003</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6499</v>
+        <v>-0.6317</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3379</v>
+        <v>-0.3411</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4645</v>
+        <v>-0.5003</v>
       </c>
       <c r="K38" t="n">
         <v>137</v>
@@ -2185,7 +2185,7 @@
         <v>87</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8024</v>
+        <v>-0.8413999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>224</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3114</v>
+        <v>-1.2756</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3596</v>
+        <v>-0.3497</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.23</v>
+        <v>-1.2049</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3114</v>
+        <v>-1.2756</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.5075</v>
+        <v>-0.4896</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5075</v>
+        <v>-0.4896</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5075</v>
+        <v>-0.4896</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="K39" t="n">
         <v>106</v>
@@ -2231,7 +2231,7 @@
         <v>74</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3114</v>
+        <v>-1.2756</v>
       </c>
       <c r="N39" t="n">
         <v>180</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3692</v>
+        <v>-0.3811</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2459</v>
+        <v>-1.257</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3466</v>
+        <v>-1.39</v>
       </c>
       <c r="N40" t="n">
         <v>108</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4326</v>
+        <v>-0.4405</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3504</v>
+        <v>-1.3556</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5779</v>
+        <v>-1.6066</v>
       </c>
       <c r="N41" t="n">
         <v>108</v>
@@ -2429,10 +2429,10 @@
         <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0098</v>
+        <v>0.951</v>
       </c>
       <c r="J2" t="n">
-        <v>27.2646</v>
+        <v>25.677</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6248</v>
+        <v>0.5997</v>
       </c>
       <c r="J3" t="n">
-        <v>16.8696</v>
+        <v>16.1919</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4751</v>
+        <v>0.4652</v>
       </c>
       <c r="J4" t="n">
-        <v>12.8277</v>
+        <v>12.5604</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2634</v>
+        <v>-0.2543</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.1118</v>
+        <v>-6.8661</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.92</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3252</v>
+        <v>-0.3121</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.7804</v>
+        <v>-8.4267</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7271</v>
+        <v>0.6957</v>
       </c>
       <c r="J7" t="n">
-        <v>19.6317</v>
+        <v>18.7839</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3108</v>
+        <v>0.3129</v>
       </c>
       <c r="J8" t="n">
-        <v>8.3916</v>
+        <v>8.4483</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1756</v>
+        <v>-0.1895</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.7412</v>
+        <v>-5.1165</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1861</v>
+        <v>-0.2</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.0247</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3154</v>
+        <v>-0.3277</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.5158</v>
+        <v>-8.847899999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2311</v>
+        <v>0.2401</v>
       </c>
       <c r="J12" t="n">
-        <v>6.4708</v>
+        <v>6.7228</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1856</v>
+        <v>0.1956</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1968</v>
+        <v>5.4768</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1043</v>
+        <v>0.1141</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9204</v>
+        <v>3.1948</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1134</v>
+        <v>-0.125</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.1752</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1579</v>
+        <v>-0.1707</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.4212</v>
+        <v>-4.7796</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6438</v>
+        <v>0.6407</v>
       </c>
       <c r="J17" t="n">
-        <v>18.0264</v>
+        <v>17.9396</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3651</v>
+        <v>0.3778</v>
       </c>
       <c r="J18" t="n">
-        <v>10.2228</v>
+        <v>10.5784</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1475</v>
+        <v>0.163</v>
       </c>
       <c r="J19" t="n">
-        <v>4.13</v>
+        <v>4.564</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.103</v>
+        <v>0.1174</v>
       </c>
       <c r="J20" t="n">
-        <v>2.884</v>
+        <v>3.2872</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.66</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3853</v>
+        <v>-0.3931</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.7884</v>
+        <v>-11.0068</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8149</v>
       </c>
       <c r="J22" t="n">
-        <v>30.4675</v>
+        <v>28.5215</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8469</v>
+        <v>0.7943</v>
       </c>
       <c r="J23" t="n">
-        <v>29.6415</v>
+        <v>27.8005</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7755</v>
+        <v>0.7318</v>
       </c>
       <c r="J24" t="n">
-        <v>27.1425</v>
+        <v>25.613</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5737</v>
+        <v>-0.5392</v>
       </c>
       <c r="J25" t="n">
-        <v>-20.0795</v>
+        <v>-18.872</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6264</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.924</v>
+        <v>-20.517</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4954</v>
+        <v>0.4857</v>
       </c>
       <c r="J27" t="n">
-        <v>17.339</v>
+        <v>16.9995</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3848</v>
+        <v>0.3831</v>
       </c>
       <c r="J28" t="n">
-        <v>13.468</v>
+        <v>13.4085</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3658</v>
+        <v>0.3654</v>
       </c>
       <c r="J29" t="n">
-        <v>12.803</v>
+        <v>12.789</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2973</v>
+        <v>-0.3099</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.4055</v>
+        <v>-10.8465</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3638</v>
+        <v>-0.3745</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.733</v>
+        <v>-13.1075</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5027</v>
+        <v>0.5622</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5729</v>
+        <v>15.1794</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.41</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4953</v>
+        <v>0.5536</v>
       </c>
       <c r="J33" t="n">
-        <v>13.3731</v>
+        <v>14.9472</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1802</v>
+        <v>-0.193</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.8654</v>
+        <v>-5.211</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2418</v>
+        <v>-0.2546</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.5286</v>
+        <v>-6.8742</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4042</v>
+        <v>-0.4128</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.9134</v>
+        <v>-11.1456</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5478</v>
+        <v>0.6222</v>
       </c>
       <c r="J37" t="n">
-        <v>14.7906</v>
+        <v>16.7994</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2501</v>
+        <v>0.2636</v>
       </c>
       <c r="J38" t="n">
-        <v>6.7527</v>
+        <v>7.1172</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.13</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2097</v>
+        <v>0.2237</v>
       </c>
       <c r="J39" t="n">
-        <v>5.6619</v>
+        <v>6.0399</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1934</v>
+        <v>-0.2057</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.2218</v>
+        <v>-5.5539</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4611</v>
+        <v>-0.4669</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.4497</v>
+        <v>-12.6063</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>29.232</v>
+        <v>31.9536</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2214</v>
+        <v>0.2252</v>
       </c>
       <c r="J43" t="n">
-        <v>7.9704</v>
+        <v>8.107200000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0051</v>
+        <v>-0.0035</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.1836</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4419</v>
+        <v>-0.4251</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.9084</v>
+        <v>-15.3036</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6554</v>
+        <v>-0.6163</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.5944</v>
+        <v>-22.1868</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2213</v>
+        <v>0.2294</v>
       </c>
       <c r="J47" t="n">
-        <v>7.9668</v>
+        <v>8.2584</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2006</v>
+        <v>0.2093</v>
       </c>
       <c r="J48" t="n">
-        <v>7.2216</v>
+        <v>7.5348</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1794</v>
+        <v>0.1886</v>
       </c>
       <c r="J49" t="n">
-        <v>6.4584</v>
+        <v>6.7896</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1578</v>
+        <v>0.1673</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6808</v>
+        <v>6.0228</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2413</v>
+        <v>-0.2542</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.6868</v>
+        <v>-9.151199999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8992</v>
+        <v>0.9943</v>
       </c>
       <c r="J52" t="n">
-        <v>21.5808</v>
+        <v>23.8632</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6585</v>
+        <v>0.7333</v>
       </c>
       <c r="J53" t="n">
-        <v>15.804</v>
+        <v>17.5992</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4438</v>
+        <v>0.4934</v>
       </c>
       <c r="J54" t="n">
-        <v>10.6512</v>
+        <v>11.8416</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4291</v>
+        <v>0.4768</v>
       </c>
       <c r="J55" t="n">
-        <v>10.2984</v>
+        <v>11.4432</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.16</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3992</v>
+        <v>0.4407</v>
       </c>
       <c r="J56" t="n">
-        <v>9.5808</v>
+        <v>10.5768</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.62</v>
+        <v>0.6774</v>
       </c>
       <c r="J57" t="n">
-        <v>14.88</v>
+        <v>16.2576</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0747</v>
+        <v>-0.0921</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.7928</v>
+        <v>-2.2104</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.65</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3572</v>
+        <v>-0.3727</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.572800000000001</v>
+        <v>-8.944800000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4228</v>
+        <v>-0.4352</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.1472</v>
+        <v>-10.4448</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.47</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5245</v>
+        <v>-0.531</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.588</v>
+        <v>-12.744</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4267</v>
+        <v>0.466</v>
       </c>
       <c r="J62" t="n">
-        <v>11.0942</v>
+        <v>12.116</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0419</v>
+        <v>-0.052</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.0894</v>
+        <v>-1.352</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.208</v>
+        <v>-0.224</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.408</v>
+        <v>-5.824</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.248</v>
+        <v>-0.2635</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.448</v>
+        <v>-6.851</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2578</v>
+        <v>-0.2732</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.7028</v>
+        <v>-7.1032</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6917</v>
+        <v>0.7651</v>
       </c>
       <c r="J67" t="n">
-        <v>17.9842</v>
+        <v>19.8926</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.22</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4988</v>
+        <v>0.552</v>
       </c>
       <c r="J68" t="n">
-        <v>12.9688</v>
+        <v>14.352</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4703</v>
+        <v>0.52</v>
       </c>
       <c r="J69" t="n">
-        <v>12.2278</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2815</v>
+        <v>0.289</v>
       </c>
       <c r="J70" t="n">
-        <v>7.319</v>
+        <v>7.514</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1738</v>
+        <v>-0.1658</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.5188</v>
+        <v>-4.3108</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4789</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>17.2404</v>
+        <v>19.6164</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4523</v>
+        <v>0.5135</v>
       </c>
       <c r="J73" t="n">
-        <v>16.2828</v>
+        <v>18.486</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.3292</v>
+        <v>-2.502</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.95</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.091</v>
+        <v>-0.0978</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.276</v>
+        <v>-3.5208</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.091</v>
+        <v>-0.0978</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.276</v>
+        <v>-3.5208</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5557</v>
+        <v>0.6226</v>
       </c>
       <c r="J77" t="n">
-        <v>20.0052</v>
+        <v>22.4136</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0275</v>
+        <v>0.033</v>
       </c>
       <c r="J78" t="n">
-        <v>0.99</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.065</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.34</v>
+        <v>-2.6604</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.83</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2107</v>
+        <v>-0.2238</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.5852</v>
+        <v>-8.056800000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2411</v>
+        <v>-0.254</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.679600000000001</v>
+        <v>-9.144</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3851</v>
+        <v>0.4127</v>
       </c>
       <c r="J82" t="n">
-        <v>9.6275</v>
+        <v>10.3175</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.0775</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1391</v>
+        <v>-0.1534</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.4775</v>
+        <v>-3.835</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.01</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1918</v>
+        <v>-0.2068</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.795</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6166</v>
+        <v>0.6814</v>
       </c>
       <c r="J87" t="n">
-        <v>15.415</v>
+        <v>17.035</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.22</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5037</v>
+        <v>0.5562</v>
       </c>
       <c r="J88" t="n">
-        <v>12.5925</v>
+        <v>13.905</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4601</v>
+        <v>0.5074</v>
       </c>
       <c r="J89" t="n">
-        <v>11.5025</v>
+        <v>12.685</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.16</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4159</v>
+        <v>0.4566</v>
       </c>
       <c r="J90" t="n">
-        <v>10.3975</v>
+        <v>11.415</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6333</v>
+        <v>-0.5911</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.8325</v>
+        <v>-14.7775</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.54</v>
       </c>
       <c r="I92" t="n">
-        <v>0.907</v>
+        <v>1.0012</v>
       </c>
       <c r="J92" t="n">
-        <v>23.582</v>
+        <v>26.0312</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.611</v>
+        <v>0.6797</v>
       </c>
       <c r="J93" t="n">
-        <v>15.886</v>
+        <v>17.6722</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.28</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="J94" t="n">
-        <v>14.8486</v>
+        <v>16.523</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1725</v>
+        <v>0.1916</v>
       </c>
       <c r="J95" t="n">
-        <v>4.485</v>
+        <v>4.9816</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1406</v>
+        <v>0.1613</v>
       </c>
       <c r="J96" t="n">
-        <v>3.6556</v>
+        <v>4.1938</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3726</v>
+        <v>0.39</v>
       </c>
       <c r="J97" t="n">
-        <v>9.6876</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0911</v>
+        <v>-0.1047</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.3686</v>
+        <v>-2.7222</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1137</v>
+        <v>-0.1283</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.9562</v>
+        <v>-3.3358</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1452</v>
+        <v>-0.1609</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.7752</v>
+        <v>-4.1834</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.62</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3994</v>
+        <v>-0.4106</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.3844</v>
+        <v>-10.6756</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2872</v>
+        <v>0.2917</v>
       </c>
       <c r="J102" t="n">
-        <v>11.7752</v>
+        <v>11.9597</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="J103" t="n">
-        <v>3.1078</v>
+        <v>3.3784</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.02</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0557</v>
+        <v>0.0613</v>
       </c>
       <c r="J104" t="n">
-        <v>2.2837</v>
+        <v>2.5133</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.018</v>
+        <v>-0.0233</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.738</v>
+        <v>-0.9553</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.407</v>
+        <v>-0.4166</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.687</v>
+        <v>-17.0806</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.35</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4136</v>
+        <v>0.4672</v>
       </c>
       <c r="J107" t="n">
-        <v>16.9576</v>
+        <v>19.1552</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2257</v>
+        <v>0.2422</v>
       </c>
       <c r="J108" t="n">
-        <v>9.2537</v>
+        <v>9.930199999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1459</v>
+        <v>0.1618</v>
       </c>
       <c r="J109" t="n">
-        <v>5.9819</v>
+        <v>6.6338</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1165</v>
+        <v>0.1318</v>
       </c>
       <c r="J110" t="n">
-        <v>4.7765</v>
+        <v>5.4038</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0329</v>
+        <v>-0.0347</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.3489</v>
+        <v>-1.4227</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0831</v>
+        <v>1.1818</v>
       </c>
       <c r="J112" t="n">
-        <v>28.1606</v>
+        <v>30.7268</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7568</v>
+        <v>0.8335</v>
       </c>
       <c r="J113" t="n">
-        <v>19.6768</v>
+        <v>21.671</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2296</v>
+        <v>-0.2227</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.9696</v>
+        <v>-5.7902</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.82</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6028</v>
+        <v>-0.5647</v>
       </c>
       <c r="J115" t="n">
-        <v>-15.6728</v>
+        <v>-14.6822</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7066</v>
+        <v>-0.6569</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.3716</v>
+        <v>-17.0794</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.39</v>
       </c>
       <c r="I117" t="n">
-        <v>0.593</v>
+        <v>0.6601</v>
       </c>
       <c r="J117" t="n">
-        <v>15.418</v>
+        <v>17.1626</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J118" t="n">
-        <v>5.3638</v>
+        <v>5.5484</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1662</v>
+        <v>-0.1797</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.3212</v>
+        <v>-4.6722</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1662</v>
+        <v>-0.1797</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.3212</v>
+        <v>-4.6722</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.76</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2779</v>
+        <v>-0.2909</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.2254</v>
+        <v>-7.5634</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.53</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9906</v>
       </c>
       <c r="J122" t="n">
-        <v>21.5448</v>
+        <v>23.7744</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6129</v>
+        <v>0.6814</v>
       </c>
       <c r="J123" t="n">
-        <v>14.7096</v>
+        <v>16.3536</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5324</v>
+        <v>0.5919</v>
       </c>
       <c r="J124" t="n">
-        <v>12.7776</v>
+        <v>14.2056</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5324</v>
+        <v>0.5919</v>
       </c>
       <c r="J125" t="n">
-        <v>12.7776</v>
+        <v>14.2056</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6047</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.5128</v>
+        <v>-13.464</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5797</v>
       </c>
       <c r="J127" t="n">
-        <v>12.6888</v>
+        <v>13.9128</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4402</v>
+        <v>0.4786</v>
       </c>
       <c r="J128" t="n">
-        <v>10.5648</v>
+        <v>11.4864</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1724</v>
+        <v>-0.1895</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.1376</v>
+        <v>-4.548</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3</v>
+        <v>-0.3157</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.2</v>
+        <v>-7.5768</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7376</v>
+        <v>-0.7281</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.7024</v>
+        <v>-17.4744</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.0921</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>2.0262</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.76</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2382</v>
+        <v>-0.2603</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.2404</v>
+        <v>-5.7266</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.71</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2868</v>
+        <v>-0.3075</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.3096</v>
+        <v>-6.765</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.53</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4523</v>
+        <v>-0.4658</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.9506</v>
+        <v>-10.2476</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.546</v>
+        <v>-0.5534</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.012</v>
+        <v>-12.1748</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5204</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>11.4488</v>
+        <v>13.1626</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4337</v>
+        <v>0.4958</v>
       </c>
       <c r="J138" t="n">
-        <v>9.541399999999999</v>
+        <v>10.9076</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4274</v>
+        <v>0.4883</v>
       </c>
       <c r="J139" t="n">
-        <v>9.402799999999999</v>
+        <v>10.7426</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.315</v>
+        <v>0.3356</v>
       </c>
       <c r="J140" t="n">
-        <v>6.93</v>
+        <v>7.3832</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.19</v>
+        <v>0.2122</v>
       </c>
       <c r="J141" t="n">
-        <v>4.18</v>
+        <v>4.6684</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7055</v>
+        <v>0.7801</v>
       </c>
       <c r="J142" t="n">
-        <v>19.754</v>
+        <v>21.8428</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4991</v>
+        <v>0.5523</v>
       </c>
       <c r="J143" t="n">
-        <v>13.9748</v>
+        <v>15.4644</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3524</v>
+        <v>0.3663</v>
       </c>
       <c r="J144" t="n">
-        <v>9.8672</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2529</v>
+        <v>0.2623</v>
       </c>
       <c r="J145" t="n">
-        <v>7.0812</v>
+        <v>7.3444</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1277</v>
+        <v>0.1437</v>
       </c>
       <c r="J146" t="n">
-        <v>3.5756</v>
+        <v>4.0236</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2927</v>
+        <v>0.2953</v>
       </c>
       <c r="J147" t="n">
-        <v>8.195600000000001</v>
+        <v>8.2684</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1888</v>
+        <v>0.1953</v>
       </c>
       <c r="J148" t="n">
-        <v>5.2864</v>
+        <v>5.4684</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0029</v>
+        <v>0.002</v>
       </c>
       <c r="J149" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1093</v>
+        <v>-0.1218</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.0604</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2563</v>
+        <v>-0.2701</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.1764</v>
+        <v>-7.5628</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3438</v>
+        <v>0.3454</v>
       </c>
       <c r="J152" t="n">
-        <v>10.314</v>
+        <v>10.362</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2656</v>
+        <v>0.2711</v>
       </c>
       <c r="J153" t="n">
-        <v>7.968</v>
+        <v>8.132999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.09</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2249</v>
+        <v>0.232</v>
       </c>
       <c r="J154" t="n">
-        <v>6.747</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1235</v>
+        <v>-0.1358</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.705</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.279</v>
+        <v>-0.2918</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.754</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0544</v>
+        <v>1.0016</v>
       </c>
       <c r="J157" t="n">
-        <v>31.632</v>
+        <v>30.048</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5991</v>
+        <v>0.577</v>
       </c>
       <c r="J158" t="n">
-        <v>17.973</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3979</v>
+        <v>0.3948</v>
       </c>
       <c r="J159" t="n">
-        <v>11.937</v>
+        <v>11.844</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2323</v>
+        <v>-0.2246</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.969</v>
+        <v>-6.738</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2645</v>
+        <v>-0.2551</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.935</v>
+        <v>-7.653</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3479</v>
+        <v>0.3597</v>
       </c>
       <c r="J162" t="n">
-        <v>9.741199999999999</v>
+        <v>10.0716</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3354</v>
+        <v>0.3477</v>
       </c>
       <c r="J163" t="n">
-        <v>9.3912</v>
+        <v>9.7356</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.18</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2719</v>
+        <v>0.2859</v>
       </c>
       <c r="J164" t="n">
-        <v>7.6132</v>
+        <v>8.0052</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1751</v>
+        <v>-0.1866</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.9028</v>
+        <v>-5.2248</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.85</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1963</v>
+        <v>-0.208</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.4964</v>
+        <v>-5.824</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.3</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4633</v>
+        <v>0.4612</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9724</v>
+        <v>12.9136</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4101</v>
+        <v>0.4115</v>
       </c>
       <c r="J168" t="n">
-        <v>11.4828</v>
+        <v>11.522</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0023</v>
+        <v>-0.0017</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.0644</v>
+        <v>-0.0476</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1916</v>
+        <v>-0.2043</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.3648</v>
+        <v>-5.7204</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2919</v>
+        <v>-0.3038</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.1732</v>
+        <v>-8.506399999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>1.035</v>
+        <v>0.9761</v>
       </c>
       <c r="J172" t="n">
-        <v>23.805</v>
+        <v>22.4503</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1095</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.1436</v>
+        <v>-2.5185</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3715</v>
+        <v>-0.3855</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.8665</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.59</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4182</v>
+        <v>-0.4301</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.618600000000001</v>
+        <v>-9.892300000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5013</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.5299</v>
+        <v>-11.6978</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1313</v>
+        <v>1.0978</v>
       </c>
       <c r="J177" t="n">
-        <v>26.0199</v>
+        <v>25.2494</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.49</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1065</v>
+        <v>1.0708</v>
       </c>
       <c r="J178" t="n">
-        <v>25.4495</v>
+        <v>24.6284</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.41</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9977</v>
+        <v>0.9458</v>
       </c>
       <c r="J179" t="n">
-        <v>22.9471</v>
+        <v>21.7534</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6128</v>
+        <v>0.5965</v>
       </c>
       <c r="J180" t="n">
-        <v>14.0944</v>
+        <v>13.7195</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4571</v>
+        <v>-0.424</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.5133</v>
+        <v>-9.752000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.68</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2662</v>
+        <v>-0.2967</v>
       </c>
       <c r="J182" t="n">
-        <v>-5.324</v>
+        <v>-5.934</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.57</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.382</v>
+        <v>-0.4052</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.64</v>
+        <v>-8.103999999999999</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.52</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4296</v>
+        <v>-0.4498</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.592000000000001</v>
+        <v>-8.996</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4296</v>
+        <v>-0.4498</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.592000000000001</v>
+        <v>-8.996</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7099</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.198</v>
+        <v>-14.144</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.93</v>
       </c>
       <c r="I187" t="n">
-        <v>1.5903</v>
+        <v>1.5912</v>
       </c>
       <c r="J187" t="n">
-        <v>31.806</v>
+        <v>31.824</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.68</v>
       </c>
       <c r="I188" t="n">
-        <v>1.3057</v>
+        <v>1.2903</v>
       </c>
       <c r="J188" t="n">
-        <v>26.114</v>
+        <v>25.806</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.51</v>
       </c>
       <c r="I189" t="n">
-        <v>1.1074</v>
+        <v>1.0769</v>
       </c>
       <c r="J189" t="n">
-        <v>22.148</v>
+        <v>21.538</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3768</v>
+        <v>0.3917</v>
       </c>
       <c r="J190" t="n">
-        <v>7.536</v>
+        <v>7.834</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2689</v>
+        <v>0.293</v>
       </c>
       <c r="J191" t="n">
-        <v>5.378</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4551</v>
+        <v>0.4493</v>
       </c>
       <c r="J192" t="n">
-        <v>13.653</v>
+        <v>13.479</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.285</v>
+        <v>0.2898</v>
       </c>
       <c r="J193" t="n">
-        <v>8.550000000000001</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J194" t="n">
-        <v>1.953</v>
+        <v>2.181</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1568</v>
+        <v>-0.1698</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.704</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2397</v>
+        <v>-0.253</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.191</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.4</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0417</v>
+        <v>0.9829</v>
       </c>
       <c r="J197" t="n">
-        <v>31.251</v>
+        <v>29.487</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6412</v>
+        <v>0.6111</v>
       </c>
       <c r="J198" t="n">
-        <v>19.236</v>
+        <v>18.333</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2129</v>
+        <v>0.2195</v>
       </c>
       <c r="J199" t="n">
-        <v>6.387</v>
+        <v>6.585</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4556</v>
+        <v>-0.4347</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.668</v>
+        <v>-13.041</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5643</v>
+        <v>-0.5326</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.929</v>
+        <v>-15.978</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1846</v>
+        <v>1.1472</v>
       </c>
       <c r="J202" t="n">
-        <v>35.538</v>
+        <v>34.416</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9892</v>
+        <v>0.9277</v>
       </c>
       <c r="J203" t="n">
-        <v>29.676</v>
+        <v>27.831</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3443</v>
+        <v>0.3455</v>
       </c>
       <c r="J204" t="n">
-        <v>10.329</v>
+        <v>10.365</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2661</v>
+        <v>-0.2562</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.983</v>
+        <v>-7.686</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.7702</v>
       </c>
       <c r="J206" t="n">
-        <v>-25.086</v>
+        <v>-23.106</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4393</v>
+        <v>0.4342</v>
       </c>
       <c r="J207" t="n">
-        <v>13.179</v>
+        <v>13.026</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.02</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0664</v>
+        <v>0.0736</v>
       </c>
       <c r="J208" t="n">
-        <v>1.992</v>
+        <v>2.208</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.98</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0358</v>
+        <v>-0.0426</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.074</v>
+        <v>-1.278</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1228</v>
+        <v>-0.1353</v>
       </c>
       <c r="J210" t="n">
-        <v>-3.684</v>
+        <v>-4.059</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1559</v>
+        <v>-0.1691</v>
       </c>
       <c r="J211" t="n">
-        <v>-4.677</v>
+        <v>-5.073</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.96</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6324</v>
+        <v>1.6339</v>
       </c>
       <c r="J212" t="n">
-        <v>34.2804</v>
+        <v>34.3119</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.78</v>
       </c>
       <c r="I213" t="n">
-        <v>1.4275</v>
+        <v>1.4185</v>
       </c>
       <c r="J213" t="n">
-        <v>29.9775</v>
+        <v>29.7885</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.4</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9615</v>
+        <v>0.913</v>
       </c>
       <c r="J214" t="n">
-        <v>20.1915</v>
+        <v>19.173</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3311</v>
+        <v>0.3485</v>
       </c>
       <c r="J215" t="n">
-        <v>6.9531</v>
+        <v>7.3185</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3673</v>
+        <v>-0.3347</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.7133</v>
+        <v>-7.0287</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.95</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0005</v>
+        <v>-0.0272</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.0105</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1949</v>
+        <v>-0.2204</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.0929</v>
+        <v>-4.6284</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.65</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3349</v>
+        <v>-0.3555</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.0329</v>
+        <v>-7.4655</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.4</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5666</v>
+        <v>-0.5735</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.8986</v>
+        <v>-12.0435</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.4</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5666</v>
+        <v>-0.5735</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.8986</v>
+        <v>-12.0435</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5582</v>
+        <v>0.5448</v>
       </c>
       <c r="J222" t="n">
-        <v>22.8862</v>
+        <v>22.3368</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="J223" t="n">
-        <v>10.7502</v>
+        <v>11.0167</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0376</v>
+        <v>-0.0439</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.5416</v>
+        <v>-1.7999</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0517</v>
+        <v>-0.0595</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.1197</v>
+        <v>-2.4395</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.76</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2806</v>
+        <v>-0.293</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.5046</v>
+        <v>-12.013</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7509</v>
+        <v>0.7059</v>
       </c>
       <c r="J227" t="n">
-        <v>30.7869</v>
+        <v>28.9419</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5747</v>
+        <v>0.55</v>
       </c>
       <c r="J228" t="n">
-        <v>23.5627</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.16</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4965</v>
+        <v>0.48</v>
       </c>
       <c r="J229" t="n">
-        <v>20.3565</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5302</v>
+        <v>-0.5034</v>
       </c>
       <c r="J230" t="n">
-        <v>-21.7382</v>
+        <v>-20.6394</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6359</v>
+        <v>-0.5978</v>
       </c>
       <c r="J231" t="n">
-        <v>-26.0719</v>
+        <v>-24.5098</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2114</v>
+        <v>0.2063</v>
       </c>
       <c r="J232" t="n">
-        <v>5.4964</v>
+        <v>5.3638</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.98</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0163</v>
+        <v>-0.0276</v>
       </c>
       <c r="J233" t="n">
-        <v>-0.4238</v>
+        <v>-0.7176</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.83</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1903</v>
+        <v>-0.2081</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.9478</v>
+        <v>-5.4106</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2973</v>
+        <v>-0.3136</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.7298</v>
+        <v>-8.153600000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3919</v>
+        <v>-0.4047</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.1894</v>
+        <v>-10.5222</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3376</v>
+        <v>1.3184</v>
       </c>
       <c r="J237" t="n">
-        <v>34.7776</v>
+        <v>34.2784</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.42</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0126</v>
+        <v>0.9624</v>
       </c>
       <c r="J238" t="n">
-        <v>26.3276</v>
+        <v>25.0224</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6818</v>
+        <v>0.6582</v>
       </c>
       <c r="J239" t="n">
-        <v>17.7268</v>
+        <v>17.1132</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.2</v>
       </c>
       <c r="I240" t="n">
-        <v>0.539</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>14.014</v>
+        <v>13.7982</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.0756</v>
+        <v>-0.0524</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.9656</v>
+        <v>-1.3624</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.99</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7324</v>
+        <v>1.7282</v>
       </c>
       <c r="J242" t="n">
-        <v>45.0424</v>
+        <v>44.9332</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.17</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4822</v>
+        <v>0.4758</v>
       </c>
       <c r="J243" t="n">
-        <v>12.5372</v>
+        <v>12.3708</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.11</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3239</v>
+        <v>0.3315</v>
       </c>
       <c r="J244" t="n">
-        <v>8.4214</v>
+        <v>8.619</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2574</v>
+        <v>-0.2422</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.6924</v>
+        <v>-6.2972</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3513</v>
+        <v>-0.3304</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.133800000000001</v>
+        <v>-8.590400000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1857</v>
+        <v>-0.2046</v>
       </c>
       <c r="J247" t="n">
-        <v>-4.8282</v>
+        <v>-5.3196</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2056</v>
+        <v>-0.2244</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.3456</v>
+        <v>-5.8344</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2056</v>
+        <v>-0.2244</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.3456</v>
+        <v>-5.8344</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2431</v>
+        <v>-0.2619</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.3206</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2621</v>
+        <v>-0.2806</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.8146</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.44</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1125</v>
+        <v>1.0633</v>
       </c>
       <c r="J252" t="n">
-        <v>33.375</v>
+        <v>31.899</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3673</v>
+        <v>0.3612</v>
       </c>
       <c r="J253" t="n">
-        <v>11.019</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2372</v>
+        <v>-0.236</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.116</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4145</v>
+        <v>-0.4001</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.435</v>
+        <v>-12.003</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6817</v>
+        <v>-0.6394</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.451</v>
+        <v>-19.182</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.23</v>
       </c>
       <c r="I257" t="n">
-        <v>0.49</v>
+        <v>0.4817</v>
       </c>
       <c r="J257" t="n">
-        <v>14.7</v>
+        <v>14.451</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J258" t="n">
-        <v>7.923</v>
+        <v>8.103</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0769</v>
+        <v>-0.0868</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.307</v>
+        <v>-2.604</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0769</v>
+        <v>-0.0868</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.307</v>
+        <v>-2.604</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2301</v>
+        <v>-0.2434</v>
       </c>
       <c r="J261" t="n">
-        <v>-6.903</v>
+        <v>-7.302</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8986</v>
+        <v>0.8347</v>
       </c>
       <c r="J262" t="n">
-        <v>26.958</v>
+        <v>25.041</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.09</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3059</v>
+        <v>0.3056</v>
       </c>
       <c r="J263" t="n">
-        <v>9.177</v>
+        <v>9.167999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.03</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1217</v>
+        <v>0.1298</v>
       </c>
       <c r="J264" t="n">
-        <v>3.651</v>
+        <v>3.894</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3031</v>
+        <v>-0.2967</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.093</v>
+        <v>-8.901</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.87</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4471</v>
+        <v>-0.4287</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.413</v>
+        <v>-12.861</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.374</v>
+        <v>0.3714</v>
       </c>
       <c r="J267" t="n">
-        <v>11.22</v>
+        <v>11.142</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.98</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0339</v>
+        <v>-0.0411</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.017</v>
+        <v>-1.233</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0339</v>
+        <v>-0.0411</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.017</v>
+        <v>-1.233</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.904</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.79</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2452</v>
+        <v>-0.2593</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.356</v>
+        <v>-7.779</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.145</v>
+        <v>1.1073</v>
       </c>
       <c r="J272" t="n">
-        <v>26.335</v>
+        <v>25.4679</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.39</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9919</v>
+        <v>0.9337</v>
       </c>
       <c r="J273" t="n">
-        <v>22.8137</v>
+        <v>21.4751</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7743</v>
+        <v>0.7353</v>
       </c>
       <c r="J274" t="n">
-        <v>17.8089</v>
+        <v>16.9119</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.04</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1227</v>
+        <v>0.1402</v>
       </c>
       <c r="J275" t="n">
-        <v>2.8221</v>
+        <v>3.2246</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8971</v>
+        <v>-0.8215</v>
       </c>
       <c r="J276" t="n">
-        <v>-20.6333</v>
+        <v>-18.8945</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.33</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7052</v>
+        <v>0.6711</v>
       </c>
       <c r="J277" t="n">
-        <v>16.2196</v>
+        <v>15.4353</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3913</v>
+        <v>0.3841</v>
       </c>
       <c r="J278" t="n">
-        <v>8.9999</v>
+        <v>8.834300000000001</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.13</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3318</v>
+        <v>0.3282</v>
       </c>
       <c r="J279" t="n">
-        <v>7.6314</v>
+        <v>7.5486</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.54</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4754</v>
+        <v>-0.4825</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.9342</v>
+        <v>-11.0975</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.44</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5654</v>
+        <v>-0.5674</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.0042</v>
+        <v>-13.0502</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.77</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0021</v>
+        <v>0.9637</v>
       </c>
       <c r="J282" t="n">
-        <v>29.0609</v>
+        <v>27.9473</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.145</v>
+        <v>0.1577</v>
       </c>
       <c r="J283" t="n">
-        <v>4.205</v>
+        <v>4.5733</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.92</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.122</v>
+        <v>-0.1316</v>
       </c>
       <c r="J284" t="n">
-        <v>-3.538</v>
+        <v>-3.8164</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1335</v>
+        <v>-0.1435</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.8715</v>
+        <v>-4.1615</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2496</v>
+        <v>-0.2607</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.2384</v>
+        <v>-7.5603</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4583</v>
+        <v>0.465</v>
       </c>
       <c r="J287" t="n">
-        <v>13.2907</v>
+        <v>13.485</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.11</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1791</v>
+        <v>0.1939</v>
       </c>
       <c r="J288" t="n">
-        <v>5.1939</v>
+        <v>5.6231</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0402</v>
+        <v>0.0495</v>
       </c>
       <c r="J289" t="n">
-        <v>1.1658</v>
+        <v>1.4355</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0426</v>
+        <v>-0.0478</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.2354</v>
+        <v>-1.3862</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1307</v>
+        <v>-0.1414</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.7903</v>
+        <v>-4.1006</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.55</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1718</v>
+        <v>1.1431</v>
       </c>
       <c r="J292" t="n">
-        <v>25.7796</v>
+        <v>25.1482</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0739</v>
+        <v>1.0354</v>
       </c>
       <c r="J293" t="n">
-        <v>23.6258</v>
+        <v>22.7788</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.42</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0055</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="J294" t="n">
-        <v>22.121</v>
+        <v>21.0342</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4546</v>
+        <v>0.4567</v>
       </c>
       <c r="J295" t="n">
-        <v>10.0012</v>
+        <v>10.0474</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.16</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4289</v>
+        <v>0.4335</v>
       </c>
       <c r="J296" t="n">
-        <v>9.4358</v>
+        <v>9.537000000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.95</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0392</v>
+        <v>-0.0577</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.2694</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1249</v>
+        <v>-0.1453</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.7478</v>
+        <v>-3.1966</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1794</v>
+        <v>-0.1997</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.9468</v>
+        <v>-4.3934</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.351</v>
+        <v>-0.3678</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.722</v>
+        <v>-8.0916</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5281</v>
+        <v>-0.5352</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.6182</v>
+        <v>-11.7744</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.89</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5385</v>
+        <v>1.5379</v>
       </c>
       <c r="J302" t="n">
-        <v>30.77</v>
+        <v>30.758</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.85</v>
       </c>
       <c r="I303" t="n">
-        <v>1.4936</v>
+        <v>1.4907</v>
       </c>
       <c r="J303" t="n">
-        <v>29.872</v>
+        <v>29.814</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9107</v>
+        <v>0.8675</v>
       </c>
       <c r="J304" t="n">
-        <v>18.214</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.25</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6182</v>
+        <v>0.6095</v>
       </c>
       <c r="J305" t="n">
-        <v>12.364</v>
+        <v>12.19</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4472</v>
+        <v>0.4567</v>
       </c>
       <c r="J306" t="n">
-        <v>8.944000000000001</v>
+        <v>9.134</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.77</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1888</v>
+        <v>-0.2196</v>
       </c>
       <c r="J307" t="n">
-        <v>-3.776</v>
+        <v>-4.392</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.76</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2001</v>
+        <v>-0.2304</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.002</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.403</v>
+        <v>-0.423</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.06</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4848</v>
+        <v>-0.4999</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.696</v>
+        <v>-9.997999999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.23</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7181</v>
+        <v>-0.7138</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.362</v>
+        <v>-14.276</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.64</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2746</v>
+        <v>1.2541</v>
       </c>
       <c r="J312" t="n">
-        <v>24.2174</v>
+        <v>23.8279</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.59</v>
       </c>
       <c r="I313" t="n">
-        <v>1.2149</v>
+        <v>1.1903</v>
       </c>
       <c r="J313" t="n">
-        <v>23.0831</v>
+        <v>22.6157</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.52</v>
       </c>
       <c r="I314" t="n">
-        <v>1.1306</v>
+        <v>1.0996</v>
       </c>
       <c r="J314" t="n">
-        <v>21.4814</v>
+        <v>20.8924</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4986</v>
+        <v>0.4977</v>
       </c>
       <c r="J315" t="n">
-        <v>9.4734</v>
+        <v>9.456300000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.98</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1875</v>
+        <v>-0.1649</v>
       </c>
       <c r="J316" t="n">
-        <v>-3.5625</v>
+        <v>-3.1331</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.08</v>
       </c>
       <c r="I317" t="n">
-        <v>0.2903</v>
+        <v>0.275</v>
       </c>
       <c r="J317" t="n">
-        <v>5.5157</v>
+        <v>5.225</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.92</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.0828</v>
+        <v>-0.1014</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.5732</v>
+        <v>-1.9266</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.76</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2505</v>
+        <v>-0.2697</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.7595</v>
+        <v>-5.1243</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.61</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3918</v>
+        <v>-0.4062</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.4442</v>
+        <v>-7.7178</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.51</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4849</v>
+        <v>-0.4943</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.213100000000001</v>
+        <v>-9.3917</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.59</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2286</v>
+        <v>1.2024</v>
       </c>
       <c r="J322" t="n">
-        <v>27.0292</v>
+        <v>26.4528</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.55</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1796</v>
+        <v>1.1499</v>
       </c>
       <c r="J323" t="n">
-        <v>25.9512</v>
+        <v>25.2978</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.23</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6115</v>
+        <v>0.5957</v>
       </c>
       <c r="J324" t="n">
-        <v>13.453</v>
+        <v>13.1054</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3859</v>
+        <v>0.3925</v>
       </c>
       <c r="J325" t="n">
-        <v>8.489800000000001</v>
+        <v>8.635</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.05</v>
       </c>
       <c r="I326" t="n">
-        <v>0.1255</v>
+        <v>0.1508</v>
       </c>
       <c r="J326" t="n">
-        <v>2.761</v>
+        <v>3.3176</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6534</v>
+        <v>0.609</v>
       </c>
       <c r="J327" t="n">
-        <v>14.3748</v>
+        <v>13.398</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.52</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.83</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1812</v>
+        <v>-0.2011</v>
       </c>
       <c r="J329" t="n">
-        <v>-3.9864</v>
+        <v>-4.4242</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.58</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4181</v>
+        <v>-0.4315</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.1982</v>
+        <v>-9.493</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.31</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6669</v>
+        <v>-0.664</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.6718</v>
+        <v>-14.608</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6348/event_6348_evp_summary.xlsx
+++ b/database/event/6348/event_6348_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0907</v>
+        <v>5.9026</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6699</v>
+        <v>1.6184</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1484</v>
+        <v>2.0831</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0907</v>
+        <v>5.9026</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2529</v>
+        <v>3.2477</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8378</v>
+        <v>2.6549</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8384</v>
+        <v>5.7508</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1527</v>
+        <v>3.2289</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8378</v>
+        <v>2.6549</v>
       </c>
       <c r="K2" t="n">
         <v>92</v>
@@ -529,7 +529,7 @@
         <v>177</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9905</v>
+        <v>5.8838</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4856</v>
+        <v>5.5491</v>
       </c>
       <c r="C3" t="n">
-        <v>1.504</v>
+        <v>1.5215</v>
       </c>
       <c r="D3" t="n">
-        <v>1.873</v>
+        <v>1.9221</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4856</v>
+        <v>5.5491</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5537</v>
+        <v>2.2177</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9319</v>
+        <v>3.3314</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5315</v>
+        <v>2.2177</v>
       </c>
       <c r="I3" t="n">
-        <v>1.907</v>
+        <v>2.2177</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9319</v>
+        <v>3.3314</v>
       </c>
       <c r="K3" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="L3" t="n">
-        <v>177</v>
+        <v>251</v>
       </c>
       <c r="M3" t="n">
-        <v>4.838900000000001</v>
+        <v>5.549099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>269</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4455</v>
+        <v>5.3099</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493</v>
+        <v>1.4559</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8547</v>
+        <v>1.8131</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4455</v>
+        <v>5.3099</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1312</v>
+        <v>2.5746</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3143</v>
+        <v>2.7353</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1312</v>
+        <v>3.2237</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1312</v>
+        <v>1.81</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3143</v>
+        <v>2.7353</v>
       </c>
       <c r="K4" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="L4" t="n">
-        <v>251</v>
+        <v>177</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4455</v>
+        <v>4.5453</v>
       </c>
       <c r="N4" t="n">
-        <v>373</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6733</v>
+        <v>4.4604</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2813</v>
+        <v>1.223</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5032</v>
+        <v>1.4261</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6733</v>
+        <v>4.4604</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2497</v>
+        <v>3.1757</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4236</v>
+        <v>1.2847</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8277</v>
+        <v>5.4804</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1469</v>
+        <v>3.0771</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4236</v>
+        <v>1.2847</v>
       </c>
       <c r="K5" t="n">
         <v>137</v>
@@ -667,7 +667,7 @@
         <v>87</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5705</v>
+        <v>4.361800000000001</v>
       </c>
       <c r="N5" t="n">
         <v>224</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8446</v>
+        <v>3.7465</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0541</v>
+        <v>1.0272</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1259</v>
+        <v>1.1009</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8446</v>
+        <v>3.7465</v>
       </c>
       <c r="F6" t="n">
-        <v>1.234</v>
+        <v>1.2281</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6106</v>
+        <v>2.5184</v>
       </c>
       <c r="H6" t="n">
-        <v>1.234</v>
+        <v>1.2281</v>
       </c>
       <c r="I6" t="n">
-        <v>1.234</v>
+        <v>1.2281</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6106</v>
+        <v>2.5184</v>
       </c>
       <c r="K6" t="n">
         <v>122</v>
@@ -713,7 +713,7 @@
         <v>251</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8446</v>
+        <v>3.7465</v>
       </c>
       <c r="N6" t="n">
         <v>373</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8095</v>
+        <v>3.7191</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0445</v>
+        <v>1.0197</v>
       </c>
       <c r="D7" t="n">
-        <v>1.11</v>
+        <v>1.0884</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8095</v>
+        <v>3.7191</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3469</v>
+        <v>3.3384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4626</v>
+        <v>0.3807</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1486</v>
+        <v>6.0913</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3202</v>
+        <v>3.4201</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4626</v>
+        <v>0.3807</v>
       </c>
       <c r="K7" t="n">
         <v>92</v>
@@ -759,7 +759,7 @@
         <v>177</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7828</v>
+        <v>3.8008</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5166</v>
+        <v>3.5043</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9608</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9766</v>
+        <v>0.9906</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5166</v>
+        <v>3.5043</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8643</v>
+        <v>1.8908</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6523</v>
+        <v>1.6135</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8643</v>
+        <v>1.8908</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8643</v>
+        <v>1.8908</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6523</v>
+        <v>1.6135</v>
       </c>
       <c r="K8" t="n">
         <v>122</v>
@@ -805,7 +805,7 @@
         <v>251</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5166</v>
+        <v>3.5043</v>
       </c>
       <c r="N8" t="n">
         <v>373</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3886</v>
+        <v>3.3533</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9291</v>
+        <v>0.9194</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9184</v>
+        <v>0.9218</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3886</v>
+        <v>3.3533</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1253</v>
+        <v>2.9981</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2633</v>
+        <v>0.3552</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1253</v>
+        <v>4.8136</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1253</v>
+        <v>2.7027</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2633</v>
+        <v>0.3552</v>
       </c>
       <c r="K9" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3886</v>
+        <v>3.0579</v>
       </c>
       <c r="N9" t="n">
-        <v>180</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3258</v>
+        <v>3.2498</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9119</v>
+        <v>0.891</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8898</v>
+        <v>0.8747</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3258</v>
+        <v>3.2498</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0372</v>
+        <v>2.104</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2886</v>
+        <v>1.1458</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1266</v>
+        <v>2.104</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7683</v>
+        <v>2.104</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2886</v>
+        <v>1.1458</v>
       </c>
       <c r="K10" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="L10" t="n">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0569</v>
+        <v>3.2498</v>
       </c>
       <c r="N10" t="n">
-        <v>269</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2376</v>
+        <v>3.0934</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8877</v>
+        <v>0.8481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8496</v>
+        <v>0.8034</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2376</v>
+        <v>3.0934</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1587</v>
+        <v>2.0984</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0789</v>
+        <v>0.995</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1587</v>
+        <v>2.0984</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1587</v>
+        <v>2.0984</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0789</v>
+        <v>0.995</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2376</v>
+        <v>3.0934</v>
       </c>
       <c r="N11" t="n">
         <v>180</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8422</v>
+        <v>2.7293</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7793</v>
+        <v>0.7483</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6696</v>
+        <v>0.6375</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8422</v>
+        <v>2.7293</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7156</v>
+        <v>2.6218</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1266</v>
+        <v>0.1076</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2186</v>
+        <v>3.0582</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3015</v>
+        <v>3.1399</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1266</v>
+        <v>0.1076</v>
       </c>
       <c r="K12" t="n">
         <v>134</v>
@@ -989,7 +989,7 @@
         <v>93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4281</v>
+        <v>3.2475</v>
       </c>
       <c r="N12" t="n">
         <v>227</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.552</v>
+        <v>2.6551</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6997</v>
+        <v>0.728</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5375</v>
+        <v>0.6037</v>
       </c>
       <c r="E13" t="n">
-        <v>2.552</v>
+        <v>2.6551</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1346</v>
+        <v>2.2337</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4174</v>
+        <v>0.4214</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1346</v>
+        <v>2.2337</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1346</v>
+        <v>2.2337</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4174</v>
+        <v>0.4214</v>
       </c>
       <c r="K13" t="n">
         <v>122</v>
@@ -1035,7 +1035,7 @@
         <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>2.552</v>
+        <v>2.6551</v>
       </c>
       <c r="N13" t="n">
         <v>373</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4527</v>
+        <v>2.5175</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6725</v>
+        <v>0.6902</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4923</v>
+        <v>0.5411</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4527</v>
+        <v>2.5175</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2979</v>
+        <v>2.3713</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1548</v>
+        <v>0.1462</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6874</v>
+        <v>2.4602</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4512</v>
+        <v>1.3813</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1548</v>
+        <v>0.1462</v>
       </c>
       <c r="K14" t="n">
         <v>137</v>
@@ -1081,7 +1081,7 @@
         <v>87</v>
       </c>
       <c r="M14" t="n">
-        <v>1.606</v>
+        <v>1.5275</v>
       </c>
       <c r="N14" t="n">
         <v>224</v>
@@ -1090,415 +1090,415 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2176</v>
+        <v>2.2322</v>
       </c>
       <c r="C15" t="n">
-        <v>0.608</v>
+        <v>0.612</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3853</v>
+        <v>0.4111</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2176</v>
+        <v>2.2322</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3608</v>
+        <v>2.7013</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8568</v>
+        <v>-0.4691</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3608</v>
+        <v>3.6992</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3959</v>
+        <v>2.077</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8568</v>
+        <v>-0.4691</v>
       </c>
       <c r="K15" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L15" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2527</v>
+        <v>1.6079</v>
       </c>
       <c r="N15" t="n">
-        <v>318</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1001</v>
+        <v>2.0451</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5758</v>
+        <v>0.5607</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3318</v>
+        <v>0.3259</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1001</v>
+        <v>2.0451</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6193</v>
+        <v>1.2587</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4808</v>
+        <v>0.7864</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6193</v>
+        <v>1.2587</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6193</v>
+        <v>1.2924</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4808</v>
+        <v>0.7864</v>
       </c>
       <c r="K16" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L16" t="n">
-        <v>251</v>
+        <v>180</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1001</v>
+        <v>2.0788</v>
       </c>
       <c r="N16" t="n">
-        <v>373</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0449</v>
+        <v>2.0133</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5607</v>
+        <v>0.552</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3067</v>
+        <v>0.3114</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0449</v>
+        <v>2.0133</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4433</v>
+        <v>0.5113</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6016</v>
+        <v>1.502</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4433</v>
+        <v>0.5113</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4433</v>
+        <v>0.5113</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6016</v>
+        <v>1.502</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0449</v>
+        <v>2.0133</v>
       </c>
       <c r="N17" t="n">
-        <v>180</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0441</v>
+        <v>2.0028</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5605</v>
+        <v>0.5491</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3063</v>
+        <v>0.3066</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0441</v>
+        <v>2.0028</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5685</v>
+        <v>1.4824</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5244</v>
+        <v>0.5204</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5802</v>
+        <v>1.4824</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9333</v>
+        <v>1.4824</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5244</v>
+        <v>0.5204</v>
       </c>
       <c r="K18" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="L18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4089</v>
+        <v>2.0028</v>
       </c>
       <c r="N18" t="n">
-        <v>224</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8844</v>
+        <v>1.8529</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5167</v>
+        <v>0.508</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2336</v>
+        <v>0.2383</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8844</v>
+        <v>1.8529</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5921</v>
+        <v>-0.2444</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2923</v>
+        <v>2.0972</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5921</v>
+        <v>-0.2444</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6074000000000001</v>
+        <v>-0.2509</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2923</v>
+        <v>2.0972</v>
       </c>
       <c r="K19" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L19" t="n">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8997</v>
+        <v>1.8463</v>
       </c>
       <c r="N19" t="n">
-        <v>227</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8677</v>
+        <v>1.8138</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5121</v>
+        <v>0.4973</v>
       </c>
       <c r="D20" t="n">
-        <v>0.226</v>
+        <v>0.2205</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8677</v>
+        <v>1.8138</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2783</v>
+        <v>2.0918</v>
       </c>
       <c r="G20" t="n">
-        <v>2.146</v>
+        <v>-0.278</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2783</v>
+        <v>2.0918</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2855</v>
+        <v>1.1745</v>
       </c>
       <c r="J20" t="n">
-        <v>2.146</v>
+        <v>-0.278</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L20" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8605</v>
+        <v>0.8965000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>318</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6474</v>
+        <v>1.5882</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4517</v>
+        <v>0.4355</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1257</v>
+        <v>0.1177</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6474</v>
+        <v>1.5882</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9724</v>
+        <v>0.4362</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.325</v>
+        <v>1.152</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9724</v>
+        <v>0.4362</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0651</v>
+        <v>0.4478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.325</v>
+        <v>1.152</v>
       </c>
       <c r="K21" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L21" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7401</v>
+        <v>1.5998</v>
       </c>
       <c r="N21" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3262</v>
+        <v>1.271</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3636</v>
+        <v>0.3485</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0205</v>
+        <v>-0.0268</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3262</v>
+        <v>1.271</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2307</v>
+        <v>2.5007</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0955</v>
+        <v>-1.2297</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2307</v>
+        <v>2.946</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2366</v>
+        <v>1.6541</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0955</v>
+        <v>-1.2297</v>
       </c>
       <c r="K22" t="n">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="L22" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3321</v>
+        <v>0.4243999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>318</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0655</v>
+        <v>1.1388</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2921</v>
+        <v>0.3122</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1392</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0655</v>
+        <v>1.1388</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3776</v>
+        <v>0.1692</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3121</v>
+        <v>0.9696</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9502</v>
+        <v>0.1692</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5931</v>
+        <v>0.1737</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3121</v>
+        <v>0.9696</v>
       </c>
       <c r="K23" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2809999999999999</v>
+        <v>1.1433</v>
       </c>
       <c r="N23" t="n">
-        <v>269</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2694</v>
+        <v>0.237</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1769</v>
+        <v>-0.2121</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9826</v>
+        <v>0.8643</v>
       </c>
       <c r="N24" t="n">
         <v>108</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1679</v>
+        <v>0.1457</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3455</v>
+        <v>-0.3638</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6122</v>
+        <v>0.5313</v>
       </c>
       <c r="N25" t="n">
         <v>108</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2646</v>
+        <v>0.1832</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0725</v>
+        <v>0.0502</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5038</v>
+        <v>-0.5223</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2646</v>
+        <v>0.1832</v>
       </c>
       <c r="F26" t="n">
-        <v>0.522</v>
+        <v>0.4414</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2574</v>
+        <v>-0.2582</v>
       </c>
       <c r="H26" t="n">
-        <v>0.522</v>
+        <v>0.4414</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5355</v>
+        <v>0.4532</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2574</v>
+        <v>-0.2582</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>93</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2781</v>
+        <v>0.195</v>
       </c>
       <c r="N26" t="n">
         <v>227</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0157</v>
+        <v>-0.0272</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6503</v>
+        <v>-0.6509</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0574</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>103</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.02</v>
+        <v>-0.0311</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6573</v>
+        <v>-0.6575</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0728</v>
+        <v>-0.1136</v>
       </c>
       <c r="N28" t="n">
         <v>103</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WOOD7</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1965</v>
+        <v>-0.229</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0539</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7137</v>
+        <v>-0.7101</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1965</v>
+        <v>-0.229</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1965</v>
+        <v>1.0789</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1.3079</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1965</v>
+        <v>1.0789</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1965</v>
+        <v>1.1077</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1.3079</v>
       </c>
       <c r="K29" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1965</v>
+        <v>-0.2002000000000002</v>
       </c>
       <c r="N29" t="n">
-        <v>103</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>WOOD7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2158</v>
+        <v>-0.3185</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0592</v>
+        <v>-0.0873</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7224</v>
+        <v>-0.7509</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2158</v>
+        <v>-0.3185</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0614</v>
+        <v>-0.3185</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.2772</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0614</v>
+        <v>-0.3185</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0887</v>
+        <v>-0.3185</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.2772</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="L30" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1884999999999999</v>
+        <v>-0.3185</v>
       </c>
       <c r="N30" t="n">
-        <v>318</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4608</v>
+        <v>-0.4327</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1263</v>
+        <v>-0.1186</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.834</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4608</v>
+        <v>-0.4327</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0992</v>
+        <v>-1.0816</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6384</v>
+        <v>0.6489</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0992</v>
+        <v>-1.0816</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.1275</v>
+        <v>-1.1105</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6384</v>
+        <v>0.6489</v>
       </c>
       <c r="K31" t="n">
         <v>138</v>
@@ -1863,7 +1863,7 @@
         <v>180</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4891</v>
+        <v>-0.4616</v>
       </c>
       <c r="N31" t="n">
         <v>318</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1455</v>
+        <v>-0.1525</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8657</v>
+        <v>-0.8592</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5305</v>
+        <v>-0.5563</v>
       </c>
       <c r="N32" t="n">
         <v>103</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7114</v>
+        <v>-0.6609</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1951</v>
+        <v>-0.1812</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.948</v>
+        <v>-0.9069</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7114</v>
+        <v>-0.6609</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6095</v>
+        <v>-0.6609</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1019</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6095</v>
+        <v>-0.6609</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6095</v>
+        <v>-0.6609</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1019</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L33" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7114</v>
+        <v>-0.6609</v>
       </c>
       <c r="N33" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7228</v>
+        <v>-0.663</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1982</v>
+        <v>-0.1818</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9532</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7228</v>
+        <v>-0.663</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7228</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7228</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7228</v>
+        <v>-0.0799</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7228</v>
+        <v>-0.6651</v>
       </c>
       <c r="N34" t="n">
-        <v>108</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7944</v>
+        <v>-0.6823</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2178</v>
+        <v>-0.1871</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9858</v>
+        <v>-0.9166</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7944</v>
+        <v>-0.6823</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1694</v>
+        <v>-0.5627</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.625</v>
+        <v>-0.1196</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1694</v>
+        <v>-0.5627</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1738</v>
+        <v>-0.5627</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.625</v>
+        <v>-0.1196</v>
       </c>
       <c r="K35" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L35" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7988</v>
+        <v>-0.6823</v>
       </c>
       <c r="N35" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8015</v>
+        <v>-0.8205</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2198</v>
+        <v>-0.225</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9891</v>
+        <v>-0.9796</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8015</v>
+        <v>-0.8205</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.042</v>
+        <v>-1.0012</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2405</v>
+        <v>0.1806</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.042</v>
+        <v>-1.0012</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0689</v>
+        <v>-1.0279</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2405</v>
+        <v>0.1806</v>
       </c>
       <c r="K36" t="n">
         <v>134</v>
@@ -2093,7 +2093,7 @@
         <v>93</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8284</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>227</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2216</v>
+        <v>-0.2332</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9921</v>
+        <v>-0.9932</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8081</v>
+        <v>-0.8504</v>
       </c>
       <c r="N37" t="n">
         <v>103</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.132</v>
+        <v>-0.8656</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3104</v>
+        <v>-0.2373</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1395</v>
+        <v>-1.0001</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.132</v>
+        <v>-0.8656</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6317</v>
+        <v>-0.4198</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5003</v>
+        <v>-0.4458</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6317</v>
+        <v>-0.4198</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3411</v>
+        <v>-0.2357</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5003</v>
+        <v>-0.4458</v>
       </c>
       <c r="K38" t="n">
         <v>137</v>
@@ -2185,7 +2185,7 @@
         <v>87</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8413999999999999</v>
+        <v>-0.6815</v>
       </c>
       <c r="N38" t="n">
         <v>224</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2756</v>
+        <v>-1.2959</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3497</v>
+        <v>-0.3553</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2049</v>
+        <v>-1.1961</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2756</v>
+        <v>-1.2959</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.4896</v>
+        <v>-0.4478</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.786</v>
+        <v>-0.8481</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4896</v>
+        <v>-0.4478</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4896</v>
+        <v>-0.4478</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.786</v>
+        <v>-0.8481</v>
       </c>
       <c r="K39" t="n">
         <v>106</v>
@@ -2231,7 +2231,7 @@
         <v>74</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2756</v>
+        <v>-1.2959</v>
       </c>
       <c r="N39" t="n">
         <v>180</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3811</v>
+        <v>-0.3716</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.257</v>
+        <v>-1.2232</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.39</v>
+        <v>-1.3554</v>
       </c>
       <c r="N40" t="n">
         <v>108</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4405</v>
+        <v>-0.4308</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3556</v>
+        <v>-1.3216</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6066</v>
+        <v>-1.5713</v>
       </c>
       <c r="N41" t="n">
         <v>108</v>
@@ -2429,10 +2429,10 @@
         <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>0.951</v>
+        <v>0.9377</v>
       </c>
       <c r="J2" t="n">
-        <v>25.677</v>
+        <v>25.3179</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5997</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>16.1919</v>
+        <v>15.201</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4652</v>
+        <v>0.4266</v>
       </c>
       <c r="J4" t="n">
-        <v>12.5604</v>
+        <v>11.5182</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2543</v>
+        <v>-0.2154</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.8661</v>
+        <v>-5.8158</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.92</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3121</v>
+        <v>-0.2708</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.4267</v>
+        <v>-7.3116</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6957</v>
+        <v>0.6399</v>
       </c>
       <c r="J7" t="n">
-        <v>18.7839</v>
+        <v>17.2773</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3129</v>
+        <v>0.2613</v>
       </c>
       <c r="J8" t="n">
-        <v>8.4483</v>
+        <v>7.0551</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1895</v>
+        <v>-0.169</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.1165</v>
+        <v>-4.563</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.85</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2</v>
+        <v>-0.1795</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.4</v>
+        <v>-4.8465</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3277</v>
+        <v>-0.3114</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.847899999999999</v>
+        <v>-8.4078</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2401</v>
+        <v>0.2248</v>
       </c>
       <c r="J12" t="n">
-        <v>6.7228</v>
+        <v>6.2944</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1956</v>
+        <v>0.1791</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4768</v>
+        <v>5.0148</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1141</v>
+        <v>0.0989</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1948</v>
+        <v>2.7692</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.92</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.125</v>
+        <v>-0.1062</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.5</v>
+        <v>-2.9736</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1707</v>
+        <v>-0.1503</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.7796</v>
+        <v>-4.2084</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6407</v>
+        <v>0.5696</v>
       </c>
       <c r="J17" t="n">
-        <v>17.9396</v>
+        <v>15.9488</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.26</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3778</v>
+        <v>0.3162</v>
       </c>
       <c r="J18" t="n">
-        <v>10.5784</v>
+        <v>8.8536</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.163</v>
+        <v>0.1264</v>
       </c>
       <c r="J19" t="n">
-        <v>4.564</v>
+        <v>3.5392</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1174</v>
+        <v>0.0886</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2872</v>
+        <v>2.4808</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.66</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3931</v>
+        <v>-0.3835</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.0068</v>
+        <v>-10.738</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.32</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8149</v>
+        <v>0.7895</v>
       </c>
       <c r="J22" t="n">
-        <v>28.5215</v>
+        <v>27.6325</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7943</v>
+        <v>0.7674</v>
       </c>
       <c r="J23" t="n">
-        <v>27.8005</v>
+        <v>26.859</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7318</v>
+        <v>0.7007</v>
       </c>
       <c r="J24" t="n">
-        <v>25.613</v>
+        <v>24.5245</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.83</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5392</v>
+        <v>-0.4991</v>
       </c>
       <c r="J25" t="n">
-        <v>-18.872</v>
+        <v>-17.4685</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5482</v>
       </c>
       <c r="J26" t="n">
-        <v>-20.517</v>
+        <v>-19.187</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4857</v>
+        <v>0.427</v>
       </c>
       <c r="J27" t="n">
-        <v>16.9995</v>
+        <v>14.945</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3831</v>
+        <v>0.3275</v>
       </c>
       <c r="J28" t="n">
-        <v>13.4085</v>
+        <v>11.4625</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3654</v>
+        <v>0.3107</v>
       </c>
       <c r="J29" t="n">
-        <v>12.789</v>
+        <v>10.8745</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.74</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3099</v>
+        <v>-0.2925</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.8465</v>
+        <v>-10.2375</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3745</v>
+        <v>-0.3618</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.1075</v>
+        <v>-12.663</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.42</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5622</v>
+        <v>0.5949</v>
       </c>
       <c r="J32" t="n">
-        <v>15.1794</v>
+        <v>16.0623</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.41</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5536</v>
+        <v>0.5856</v>
       </c>
       <c r="J33" t="n">
-        <v>14.9472</v>
+        <v>15.8112</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.193</v>
+        <v>-0.1724</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.211</v>
+        <v>-4.6548</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2546</v>
+        <v>-0.2348</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.8742</v>
+        <v>-6.3396</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4128</v>
+        <v>-0.4041</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.1456</v>
+        <v>-10.9107</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.53</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6222</v>
+        <v>0.5851</v>
       </c>
       <c r="J37" t="n">
-        <v>16.7994</v>
+        <v>15.7977</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2636</v>
+        <v>0.2118</v>
       </c>
       <c r="J38" t="n">
-        <v>7.1172</v>
+        <v>5.7186</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.13</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2237</v>
+        <v>0.1767</v>
       </c>
       <c r="J39" t="n">
-        <v>6.0399</v>
+        <v>4.7709</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2057</v>
+        <v>-0.1851</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.5539</v>
+        <v>-4.9977</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4669</v>
+        <v>-0.4648</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.6063</v>
+        <v>-12.5496</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8747</v>
       </c>
       <c r="J42" t="n">
-        <v>31.9536</v>
+        <v>31.4892</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2252</v>
+        <v>0.19</v>
       </c>
       <c r="J43" t="n">
-        <v>8.107200000000001</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0035</v>
+        <v>-0.0018</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.126</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4251</v>
+        <v>-0.382</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.3036</v>
+        <v>-13.752</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.79</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6163</v>
+        <v>-0.5784</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.1868</v>
+        <v>-20.8224</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.09</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2294</v>
+        <v>0.1856</v>
       </c>
       <c r="J47" t="n">
-        <v>8.2584</v>
+        <v>6.6816</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2093</v>
+        <v>0.1677</v>
       </c>
       <c r="J48" t="n">
-        <v>7.5348</v>
+        <v>6.0372</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1886</v>
+        <v>0.1495</v>
       </c>
       <c r="J49" t="n">
-        <v>6.7896</v>
+        <v>5.382</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1673</v>
+        <v>0.131</v>
       </c>
       <c r="J50" t="n">
-        <v>6.0228</v>
+        <v>4.716</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2542</v>
+        <v>-0.2344</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.151199999999999</v>
+        <v>-8.4384</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9943</v>
+        <v>0.9818</v>
       </c>
       <c r="J52" t="n">
-        <v>23.8632</v>
+        <v>23.5632</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7333</v>
+        <v>0.7209</v>
       </c>
       <c r="J53" t="n">
-        <v>17.5992</v>
+        <v>17.3016</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.19</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4934</v>
+        <v>0.4812</v>
       </c>
       <c r="J54" t="n">
-        <v>11.8416</v>
+        <v>11.5488</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.18</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4768</v>
+        <v>0.4589</v>
       </c>
       <c r="J55" t="n">
-        <v>11.4432</v>
+        <v>11.0136</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.16</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4407</v>
+        <v>0.4124</v>
       </c>
       <c r="J56" t="n">
-        <v>10.5768</v>
+        <v>9.897600000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6774</v>
+        <v>0.6596</v>
       </c>
       <c r="J57" t="n">
-        <v>16.2576</v>
+        <v>15.8304</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0921</v>
+        <v>-0.0785</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2104</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.65</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3727</v>
+        <v>-0.3591</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.944800000000001</v>
+        <v>-8.618399999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.58</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4352</v>
+        <v>-0.4268</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.4448</v>
+        <v>-10.2432</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.47</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.531</v>
+        <v>-0.5344</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.744</v>
+        <v>-12.8256</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.466</v>
+        <v>0.4196</v>
       </c>
       <c r="J62" t="n">
-        <v>12.116</v>
+        <v>10.9096</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.052</v>
+        <v>-0.0419</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.352</v>
+        <v>-1.0894</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.82</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.224</v>
+        <v>-0.204</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.824</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2635</v>
+        <v>-0.2441</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.851</v>
+        <v>-6.3466</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2732</v>
+        <v>-0.2541</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.1032</v>
+        <v>-6.6066</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7651</v>
+        <v>0.7494</v>
       </c>
       <c r="J67" t="n">
-        <v>19.8926</v>
+        <v>19.4844</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.22</v>
       </c>
       <c r="I68" t="n">
-        <v>0.552</v>
+        <v>0.5435</v>
       </c>
       <c r="J68" t="n">
-        <v>14.352</v>
+        <v>14.131</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.52</v>
+        <v>0.5093</v>
       </c>
       <c r="J69" t="n">
-        <v>13.52</v>
+        <v>13.2418</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.09</v>
       </c>
       <c r="I70" t="n">
-        <v>0.289</v>
+        <v>0.2562</v>
       </c>
       <c r="J70" t="n">
-        <v>7.514</v>
+        <v>6.6612</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.97</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1658</v>
+        <v>-0.1343</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.3108</v>
+        <v>-3.4918</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5081</v>
       </c>
       <c r="J72" t="n">
-        <v>19.6164</v>
+        <v>18.2916</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5135</v>
+        <v>0.47</v>
       </c>
       <c r="J73" t="n">
-        <v>18.486</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0553</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.502</v>
+        <v>-1.9908</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.95</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0978</v>
+        <v>-0.0808</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.5208</v>
+        <v>-2.9088</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0978</v>
+        <v>-0.0808</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.5208</v>
+        <v>-2.9088</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.49</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6226</v>
+        <v>0.6609</v>
       </c>
       <c r="J77" t="n">
-        <v>22.4136</v>
+        <v>23.7924</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.033</v>
+        <v>0.0254</v>
       </c>
       <c r="J78" t="n">
-        <v>1.188</v>
+        <v>0.9144</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.6604</v>
+        <v>-2.1312</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.83</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2238</v>
+        <v>-0.2033</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.056800000000001</v>
+        <v>-7.3188</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.254</v>
+        <v>-0.2343</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.144</v>
+        <v>-8.434799999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4127</v>
+        <v>0.357</v>
       </c>
       <c r="J82" t="n">
-        <v>10.3175</v>
+        <v>8.925000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.38</v>
+        <v>-1.9925</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1534</v>
+        <v>-0.1342</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.835</v>
+        <v>-3.355</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1752</v>
+        <v>-0.1553</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.38</v>
+        <v>-3.8825</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2068</v>
+        <v>-0.1865</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.17</v>
+        <v>-4.6625</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6814</v>
+        <v>0.6667</v>
       </c>
       <c r="J87" t="n">
-        <v>17.035</v>
+        <v>16.6675</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.22</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5562</v>
+        <v>0.5466</v>
       </c>
       <c r="J88" t="n">
-        <v>13.905</v>
+        <v>13.665</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.19</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5074</v>
+        <v>0.4925</v>
       </c>
       <c r="J89" t="n">
-        <v>12.685</v>
+        <v>12.3125</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.16</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4566</v>
+        <v>0.4258</v>
       </c>
       <c r="J90" t="n">
-        <v>11.415</v>
+        <v>10.645</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5911</v>
+        <v>-0.5538</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.7775</v>
+        <v>-13.845</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.54</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0012</v>
+        <v>0.9887</v>
       </c>
       <c r="J92" t="n">
-        <v>26.0312</v>
+        <v>25.7062</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.31</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6797</v>
+        <v>0.6679</v>
       </c>
       <c r="J93" t="n">
-        <v>17.6722</v>
+        <v>17.3654</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.28</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6355</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>16.523</v>
+        <v>16.263</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1916</v>
+        <v>0.1638</v>
       </c>
       <c r="J95" t="n">
-        <v>4.9816</v>
+        <v>4.2588</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.05</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1613</v>
+        <v>0.1354</v>
       </c>
       <c r="J96" t="n">
-        <v>4.1938</v>
+        <v>3.5204</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.16</v>
       </c>
       <c r="I97" t="n">
-        <v>0.39</v>
+        <v>0.3358</v>
       </c>
       <c r="J97" t="n">
-        <v>10.14</v>
+        <v>8.7308</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1047</v>
+        <v>-0.0896</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.7222</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1283</v>
+        <v>-0.1114</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.3358</v>
+        <v>-2.8964</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1609</v>
+        <v>-0.1424</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.1834</v>
+        <v>-3.7024</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.62</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4106</v>
+        <v>-0.4005</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.6756</v>
+        <v>-10.413</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2917</v>
+        <v>0.279</v>
       </c>
       <c r="J102" t="n">
-        <v>11.9597</v>
+        <v>11.439</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.03</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0824</v>
+        <v>0.068</v>
       </c>
       <c r="J103" t="n">
-        <v>3.3784</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.02</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0613</v>
+        <v>0.0489</v>
       </c>
       <c r="J104" t="n">
-        <v>2.5133</v>
+        <v>2.0049</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0233</v>
+        <v>-0.0172</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.9553</v>
+        <v>-0.7052</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4166</v>
+        <v>-0.4077</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.0806</v>
+        <v>-16.7157</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.35</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4672</v>
+        <v>0.4099</v>
       </c>
       <c r="J107" t="n">
-        <v>19.1552</v>
+        <v>16.8059</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.15</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2422</v>
+        <v>0.1946</v>
       </c>
       <c r="J108" t="n">
-        <v>9.930199999999999</v>
+        <v>7.9786</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.09</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1618</v>
+        <v>0.1257</v>
       </c>
       <c r="J109" t="n">
-        <v>6.6338</v>
+        <v>5.1537</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1318</v>
+        <v>0.1007</v>
       </c>
       <c r="J110" t="n">
-        <v>5.4038</v>
+        <v>4.1287</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.99</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0347</v>
+        <v>-0.0255</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.4227</v>
+        <v>-1.0455</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.65</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1818</v>
+        <v>1.1815</v>
       </c>
       <c r="J112" t="n">
-        <v>30.7268</v>
+        <v>30.719</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.4</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8335</v>
+        <v>0.8176</v>
       </c>
       <c r="J113" t="n">
-        <v>21.671</v>
+        <v>21.2576</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2227</v>
+        <v>-0.1857</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.7902</v>
+        <v>-4.8282</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.82</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5647</v>
+        <v>-0.5259</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.6822</v>
+        <v>-13.6734</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6569</v>
+        <v>-0.623</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.0794</v>
+        <v>-16.198</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.39</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6601</v>
+        <v>0.6296</v>
       </c>
       <c r="J117" t="n">
-        <v>17.1626</v>
+        <v>16.3696</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J118" t="n">
-        <v>5.5484</v>
+        <v>4.4408</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1797</v>
+        <v>-0.1592</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.6722</v>
+        <v>-4.1392</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1797</v>
+        <v>-0.1592</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.6722</v>
+        <v>-4.1392</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.76</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2909</v>
+        <v>-0.2725</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.5634</v>
+        <v>-7.085</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.53</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9906</v>
+        <v>0.9777</v>
       </c>
       <c r="J122" t="n">
-        <v>23.7744</v>
+        <v>23.4648</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.31</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6814</v>
+        <v>0.669</v>
       </c>
       <c r="J123" t="n">
-        <v>16.3536</v>
+        <v>16.056</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.25</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5919</v>
+        <v>0.5837</v>
       </c>
       <c r="J124" t="n">
-        <v>14.2056</v>
+        <v>14.0088</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5919</v>
+        <v>0.5837</v>
       </c>
       <c r="J125" t="n">
-        <v>14.2056</v>
+        <v>14.0088</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5248</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.464</v>
+        <v>-12.5952</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5797</v>
+        <v>0.5588</v>
       </c>
       <c r="J127" t="n">
-        <v>13.9128</v>
+        <v>13.4112</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4786</v>
+        <v>0.4392</v>
       </c>
       <c r="J128" t="n">
-        <v>11.4864</v>
+        <v>10.5408</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.85</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1895</v>
+        <v>-0.171</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.548</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3157</v>
+        <v>-0.2985</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.5768</v>
+        <v>-7.164</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7281</v>
+        <v>-0.7687</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.4744</v>
+        <v>-18.4488</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>1.518</v>
+        <v>1.7314</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.76</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2603</v>
+        <v>-0.2462</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.7266</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.71</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3075</v>
+        <v>-0.2943</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.765</v>
+        <v>-6.4746</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.53</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4658</v>
+        <v>-0.4604</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.2476</v>
+        <v>-10.1288</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.43</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5534</v>
+        <v>-0.5586</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.1748</v>
+        <v>-12.2892</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.55</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5618</v>
       </c>
       <c r="J137" t="n">
-        <v>13.1626</v>
+        <v>12.3596</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.41</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4958</v>
+        <v>0.45</v>
       </c>
       <c r="J138" t="n">
-        <v>10.9076</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.4</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4883</v>
+        <v>0.4404</v>
       </c>
       <c r="J139" t="n">
-        <v>10.7426</v>
+        <v>9.688800000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3356</v>
+        <v>0.2826</v>
       </c>
       <c r="J140" t="n">
-        <v>7.3832</v>
+        <v>6.2172</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.14</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2122</v>
+        <v>0.1713</v>
       </c>
       <c r="J141" t="n">
-        <v>4.6684</v>
+        <v>3.7686</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7801</v>
+        <v>0.7642</v>
       </c>
       <c r="J142" t="n">
-        <v>21.8428</v>
+        <v>21.3976</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5523</v>
+        <v>0.5437</v>
       </c>
       <c r="J143" t="n">
-        <v>15.4644</v>
+        <v>15.2236</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.12</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3663</v>
+        <v>0.3311</v>
       </c>
       <c r="J144" t="n">
-        <v>10.2564</v>
+        <v>9.270799999999999</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2623</v>
+        <v>0.2305</v>
       </c>
       <c r="J145" t="n">
-        <v>7.3444</v>
+        <v>6.454</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1437</v>
+        <v>0.1196</v>
       </c>
       <c r="J146" t="n">
-        <v>4.0236</v>
+        <v>3.3488</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2953</v>
+        <v>0.245</v>
       </c>
       <c r="J147" t="n">
-        <v>8.2684</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.07</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1953</v>
+        <v>0.1546</v>
       </c>
       <c r="J148" t="n">
-        <v>5.4684</v>
+        <v>4.3288</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.002</v>
+        <v>0.0009</v>
       </c>
       <c r="J149" t="n">
-        <v>0.056</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.92</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1218</v>
+        <v>-0.1037</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.4104</v>
+        <v>-2.9036</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.78</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2701</v>
+        <v>-0.2507</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.5628</v>
+        <v>-7.0196</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3454</v>
+        <v>0.2918</v>
       </c>
       <c r="J152" t="n">
-        <v>10.362</v>
+        <v>8.754</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2711</v>
+        <v>0.223</v>
       </c>
       <c r="J153" t="n">
-        <v>8.132999999999999</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.09</v>
       </c>
       <c r="I154" t="n">
-        <v>0.232</v>
+        <v>0.1876</v>
       </c>
       <c r="J154" t="n">
-        <v>6.96</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1358</v>
+        <v>-0.1166</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.074</v>
+        <v>-3.498</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2918</v>
+        <v>-0.2735</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.754</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.42</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0016</v>
+        <v>0.9987</v>
       </c>
       <c r="J157" t="n">
-        <v>30.048</v>
+        <v>29.961</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.577</v>
+        <v>0.5399</v>
       </c>
       <c r="J158" t="n">
-        <v>17.31</v>
+        <v>16.197</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3948</v>
+        <v>0.3572</v>
       </c>
       <c r="J159" t="n">
-        <v>11.844</v>
+        <v>10.716</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.95</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2246</v>
+        <v>-0.1875</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.738</v>
+        <v>-5.625</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2551</v>
+        <v>-0.2162</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.653</v>
+        <v>-6.486</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.24</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3597</v>
+        <v>0.2991</v>
       </c>
       <c r="J162" t="n">
-        <v>10.0716</v>
+        <v>8.3748</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.23</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3477</v>
+        <v>0.288</v>
       </c>
       <c r="J163" t="n">
-        <v>9.7356</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.18</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2859</v>
+        <v>0.2321</v>
       </c>
       <c r="J164" t="n">
-        <v>8.0052</v>
+        <v>6.4988</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1866</v>
+        <v>-0.1661</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.2248</v>
+        <v>-4.6508</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.85</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.208</v>
+        <v>-0.1874</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.824</v>
+        <v>-5.2472</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.3</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4612</v>
+        <v>0.4653</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9136</v>
+        <v>13.0284</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4115</v>
+        <v>0.4096</v>
       </c>
       <c r="J168" t="n">
-        <v>11.522</v>
+        <v>11.4688</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0017</v>
+        <v>-0.0009</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.0476</v>
+        <v>-0.0252</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.85</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2043</v>
+        <v>-0.1837</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.7204</v>
+        <v>-5.1436</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.75</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3038</v>
+        <v>-0.2863</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.506399999999999</v>
+        <v>-8.016400000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.5</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9761</v>
+        <v>0.9633</v>
       </c>
       <c r="J172" t="n">
-        <v>22.4503</v>
+        <v>22.1559</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.92</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1095</v>
+        <v>-0.095</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.5185</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3855</v>
+        <v>-0.3728</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.8665</v>
+        <v>-8.574400000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.59</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4301</v>
+        <v>-0.4214</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.892300000000001</v>
+        <v>-9.6922</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5092</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.6978</v>
+        <v>-11.7116</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>1.0978</v>
+        <v>1.1098</v>
       </c>
       <c r="J177" t="n">
-        <v>25.2494</v>
+        <v>25.5254</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.49</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0708</v>
+        <v>1.0805</v>
       </c>
       <c r="J178" t="n">
-        <v>24.6284</v>
+        <v>24.8515</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.41</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9458</v>
+        <v>0.9375</v>
       </c>
       <c r="J179" t="n">
-        <v>21.7534</v>
+        <v>21.5625</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.23</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5965</v>
+        <v>0.5685</v>
       </c>
       <c r="J180" t="n">
-        <v>13.7195</v>
+        <v>13.0755</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.89</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.424</v>
+        <v>-0.3859</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.752000000000001</v>
+        <v>-8.8757</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.68</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2967</v>
+        <v>-0.2839</v>
       </c>
       <c r="J182" t="n">
-        <v>-5.934</v>
+        <v>-5.678</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.57</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4052</v>
+        <v>-0.4016</v>
       </c>
       <c r="J183" t="n">
-        <v>-8.103999999999999</v>
+        <v>-8.032</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.52</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4498</v>
+        <v>-0.4481</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.996</v>
+        <v>-8.962</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4498</v>
+        <v>-0.4481</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.996</v>
+        <v>-8.962</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.23</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.7372</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.144</v>
+        <v>-14.744</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.93</v>
       </c>
       <c r="I187" t="n">
-        <v>1.5912</v>
+        <v>1.6295</v>
       </c>
       <c r="J187" t="n">
-        <v>31.824</v>
+        <v>32.59</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.68</v>
       </c>
       <c r="I188" t="n">
-        <v>1.2903</v>
+        <v>1.311</v>
       </c>
       <c r="J188" t="n">
-        <v>25.806</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.51</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0769</v>
+        <v>1.0925</v>
       </c>
       <c r="J189" t="n">
-        <v>21.538</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.15</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3917</v>
+        <v>0.3594</v>
       </c>
       <c r="J190" t="n">
-        <v>7.834</v>
+        <v>7.188</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.11</v>
       </c>
       <c r="I191" t="n">
-        <v>0.293</v>
+        <v>0.2596</v>
       </c>
       <c r="J191" t="n">
-        <v>5.86</v>
+        <v>5.192</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.21</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4493</v>
+        <v>0.3912</v>
       </c>
       <c r="J192" t="n">
-        <v>13.479</v>
+        <v>11.736</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2898</v>
+        <v>0.2401</v>
       </c>
       <c r="J193" t="n">
-        <v>8.694000000000001</v>
+        <v>7.203</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0727</v>
+        <v>0.0521</v>
       </c>
       <c r="J194" t="n">
-        <v>2.181</v>
+        <v>1.563</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1698</v>
+        <v>-0.1495</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.094</v>
+        <v>-4.485</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.8</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.253</v>
+        <v>-0.2331</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.59</v>
+        <v>-6.993</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.4</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9829</v>
+        <v>0.9774</v>
       </c>
       <c r="J197" t="n">
-        <v>29.487</v>
+        <v>29.322</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.22</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6111</v>
+        <v>0.5733</v>
       </c>
       <c r="J198" t="n">
-        <v>18.333</v>
+        <v>17.199</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2195</v>
+        <v>0.1871</v>
       </c>
       <c r="J199" t="n">
-        <v>6.585</v>
+        <v>5.613</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4347</v>
+        <v>-0.3918</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.041</v>
+        <v>-11.754</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.83</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5326</v>
+        <v>-0.4918</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.978</v>
+        <v>-14.754</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1472</v>
+        <v>1.161</v>
       </c>
       <c r="J202" t="n">
-        <v>34.416</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.38</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9277</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>27.831</v>
+        <v>27.384</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.11</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3455</v>
+        <v>0.3095</v>
       </c>
       <c r="J204" t="n">
-        <v>10.365</v>
+        <v>9.285</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2562</v>
+        <v>-0.2173</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.686</v>
+        <v>-6.519</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7702</v>
+        <v>-0.7454</v>
       </c>
       <c r="J206" t="n">
-        <v>-23.106</v>
+        <v>-22.362</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.2</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4342</v>
+        <v>0.3766</v>
       </c>
       <c r="J207" t="n">
-        <v>13.026</v>
+        <v>11.298</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.02</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0736</v>
+        <v>0.0526</v>
       </c>
       <c r="J208" t="n">
-        <v>2.208</v>
+        <v>1.578</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.98</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0426</v>
+        <v>-0.0324</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.278</v>
+        <v>-0.972</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.91</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1353</v>
+        <v>-0.1161</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.059</v>
+        <v>-3.483</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.88</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1691</v>
+        <v>-0.1488</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.073</v>
+        <v>-4.464</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.96</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6339</v>
+        <v>1.6761</v>
       </c>
       <c r="J212" t="n">
-        <v>34.3119</v>
+        <v>35.1981</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.78</v>
       </c>
       <c r="I213" t="n">
-        <v>1.4185</v>
+        <v>1.4446</v>
       </c>
       <c r="J213" t="n">
-        <v>29.7885</v>
+        <v>30.3366</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.4</v>
       </c>
       <c r="I214" t="n">
-        <v>0.913</v>
+        <v>0.9077</v>
       </c>
       <c r="J214" t="n">
-        <v>19.173</v>
+        <v>19.0617</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3485</v>
+        <v>0.3159</v>
       </c>
       <c r="J215" t="n">
-        <v>7.3185</v>
+        <v>6.6339</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3347</v>
+        <v>-0.3017</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.0287</v>
+        <v>-6.3357</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.95</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0272</v>
+        <v>-0.0073</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.5712</v>
+        <v>-0.1533</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.79</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2204</v>
+        <v>-0.2054</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.6284</v>
+        <v>-4.3134</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.65</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3555</v>
+        <v>-0.3449</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.4655</v>
+        <v>-7.2429</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.4</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5735</v>
+        <v>-0.5812</v>
       </c>
       <c r="J220" t="n">
-        <v>-12.0435</v>
+        <v>-12.2052</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.4</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5735</v>
+        <v>-0.5812</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.0435</v>
+        <v>-12.2052</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.27</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5448</v>
+        <v>0.4853</v>
       </c>
       <c r="J222" t="n">
-        <v>22.3368</v>
+        <v>19.8973</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2687</v>
+        <v>0.221</v>
       </c>
       <c r="J223" t="n">
-        <v>11.0167</v>
+        <v>9.061</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.98</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0439</v>
+        <v>-0.0332</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.7999</v>
+        <v>-1.3612</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.97</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0595</v>
+        <v>-0.0465</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.4395</v>
+        <v>-1.9065</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.76</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.293</v>
+        <v>-0.2748</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.013</v>
+        <v>-11.2668</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.26</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7059</v>
+        <v>0.6727</v>
       </c>
       <c r="J227" t="n">
-        <v>28.9419</v>
+        <v>27.5807</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.19</v>
       </c>
       <c r="I228" t="n">
-        <v>0.55</v>
+        <v>0.5097</v>
       </c>
       <c r="J228" t="n">
-        <v>22.55</v>
+        <v>20.8977</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.16</v>
       </c>
       <c r="I229" t="n">
-        <v>0.48</v>
+        <v>0.4384</v>
       </c>
       <c r="J229" t="n">
-        <v>19.68</v>
+        <v>17.9744</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5034</v>
+        <v>-0.4615</v>
       </c>
       <c r="J230" t="n">
-        <v>-20.6394</v>
+        <v>-18.9215</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5978</v>
+        <v>-0.5593</v>
       </c>
       <c r="J231" t="n">
-        <v>-24.5098</v>
+        <v>-22.9313</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2063</v>
+        <v>0.1665</v>
       </c>
       <c r="J232" t="n">
-        <v>5.3638</v>
+        <v>4.329</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.98</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0276</v>
+        <v>-0.0204</v>
       </c>
       <c r="J233" t="n">
-        <v>-0.7176</v>
+        <v>-0.5304</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.83</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2081</v>
+        <v>-0.1897</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.4106</v>
+        <v>-4.9322</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.72</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3136</v>
+        <v>-0.2965</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.153600000000001</v>
+        <v>-7.709</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.62</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4047</v>
+        <v>-0.3937</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.5222</v>
+        <v>-10.2362</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.68</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3184</v>
+        <v>1.3386</v>
       </c>
       <c r="J237" t="n">
-        <v>34.2784</v>
+        <v>34.8036</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.42</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9624</v>
+        <v>0.9565</v>
       </c>
       <c r="J238" t="n">
-        <v>25.0224</v>
+        <v>24.869</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6582</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>17.1132</v>
+        <v>16.4476</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.2</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="J240" t="n">
-        <v>13.7982</v>
+        <v>13.026</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.0524</v>
+        <v>-0.0481</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.3624</v>
+        <v>-1.2506</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.99</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7282</v>
+        <v>1.7878</v>
       </c>
       <c r="J242" t="n">
-        <v>44.9332</v>
+        <v>46.4828</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.17</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4758</v>
+        <v>0.4424</v>
       </c>
       <c r="J243" t="n">
-        <v>12.3708</v>
+        <v>11.5024</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.11</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3315</v>
+        <v>0.2988</v>
       </c>
       <c r="J244" t="n">
-        <v>8.619</v>
+        <v>7.7688</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2422</v>
+        <v>-0.206</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.2972</v>
+        <v>-5.356</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3304</v>
+        <v>-0.2907</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.590400000000001</v>
+        <v>-7.5582</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.83</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2046</v>
+        <v>-0.1878</v>
       </c>
       <c r="J247" t="n">
-        <v>-5.3196</v>
+        <v>-4.8828</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2244</v>
+        <v>-0.2073</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.8344</v>
+        <v>-5.3898</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2244</v>
+        <v>-0.2073</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.8344</v>
+        <v>-5.3898</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2619</v>
+        <v>-0.2445</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.8094</v>
+        <v>-6.357</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2806</v>
+        <v>-0.2633</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.2956</v>
+        <v>-6.8458</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.44</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0633</v>
+        <v>1.074</v>
       </c>
       <c r="J252" t="n">
-        <v>31.899</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3612</v>
+        <v>0.3196</v>
       </c>
       <c r="J253" t="n">
-        <v>10.836</v>
+        <v>9.587999999999999</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.236</v>
+        <v>-0.1983</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.08</v>
+        <v>-5.949</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4001</v>
+        <v>-0.357</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.003</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.78</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6394</v>
+        <v>-0.6029</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.182</v>
+        <v>-18.087</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.23</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4817</v>
+        <v>0.4229</v>
       </c>
       <c r="J257" t="n">
-        <v>14.451</v>
+        <v>12.687</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J258" t="n">
-        <v>8.103</v>
+        <v>6.663</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.95</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0868</v>
+        <v>-0.0709</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.604</v>
+        <v>-2.127</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0868</v>
+        <v>-0.0709</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.604</v>
+        <v>-2.127</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2434</v>
+        <v>-0.2232</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.302</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.32</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8347</v>
+        <v>0.8113</v>
       </c>
       <c r="J262" t="n">
-        <v>25.041</v>
+        <v>24.339</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.09</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3056</v>
+        <v>0.2666</v>
       </c>
       <c r="J263" t="n">
-        <v>9.167999999999999</v>
+        <v>7.998</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.03</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1298</v>
+        <v>0.1048</v>
       </c>
       <c r="J264" t="n">
-        <v>3.894</v>
+        <v>3.144</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.92</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2967</v>
+        <v>-0.2556</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.901</v>
+        <v>-7.668</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.87</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4287</v>
+        <v>-0.3856</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.861</v>
+        <v>-11.568</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.16</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3714</v>
+        <v>0.3164</v>
       </c>
       <c r="J267" t="n">
-        <v>11.142</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.98</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0411</v>
+        <v>-0.0317</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.233</v>
+        <v>-0.951</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.98</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0411</v>
+        <v>-0.0317</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.233</v>
+        <v>-0.951</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.93</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J270" t="n">
-        <v>-3.27</v>
+        <v>-2.757</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.79</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2593</v>
+        <v>-0.2396</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.779</v>
+        <v>-7.188</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1073</v>
+        <v>1.1189</v>
       </c>
       <c r="J272" t="n">
-        <v>25.4679</v>
+        <v>25.7347</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.39</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9337</v>
+        <v>0.92</v>
       </c>
       <c r="J273" t="n">
-        <v>21.4751</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.29</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7353</v>
+        <v>0.7067</v>
       </c>
       <c r="J274" t="n">
-        <v>16.9119</v>
+        <v>16.2541</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.04</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1402</v>
+        <v>0.1164</v>
       </c>
       <c r="J275" t="n">
-        <v>3.2246</v>
+        <v>2.6772</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8215</v>
+        <v>-0.8028</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.8945</v>
+        <v>-18.4644</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.33</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6711</v>
+        <v>0.6179</v>
       </c>
       <c r="J277" t="n">
-        <v>15.4353</v>
+        <v>14.2117</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3841</v>
+        <v>0.3294</v>
       </c>
       <c r="J278" t="n">
-        <v>8.834300000000001</v>
+        <v>7.5762</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.13</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3282</v>
+        <v>0.2762</v>
       </c>
       <c r="J279" t="n">
-        <v>7.5486</v>
+        <v>6.3526</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.54</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4825</v>
+        <v>-0.4808</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.0975</v>
+        <v>-11.0584</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.44</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5674</v>
+        <v>-0.578</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.0502</v>
+        <v>-13.294</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.77</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9637</v>
+        <v>1.0578</v>
       </c>
       <c r="J282" t="n">
-        <v>27.9473</v>
+        <v>30.6762</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1577</v>
+        <v>0.1435</v>
       </c>
       <c r="J283" t="n">
-        <v>4.5733</v>
+        <v>4.1615</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.92</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1316</v>
+        <v>-0.1124</v>
       </c>
       <c r="J284" t="n">
-        <v>-3.8164</v>
+        <v>-3.2596</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.91</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1435</v>
+        <v>-0.1238</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.1615</v>
+        <v>-3.5902</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2607</v>
+        <v>-0.2416</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.5603</v>
+        <v>-7.0064</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I287" t="n">
-        <v>0.465</v>
+        <v>0.3981</v>
       </c>
       <c r="J287" t="n">
-        <v>13.485</v>
+        <v>11.5449</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.11</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1939</v>
+        <v>0.1514</v>
       </c>
       <c r="J288" t="n">
-        <v>5.6231</v>
+        <v>4.3906</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0495</v>
+        <v>0.0344</v>
       </c>
       <c r="J289" t="n">
-        <v>1.4355</v>
+        <v>0.9976</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0478</v>
+        <v>-0.0362</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.3862</v>
+        <v>-1.0498</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.91</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1414</v>
+        <v>-0.1217</v>
       </c>
       <c r="J291" t="n">
-        <v>-4.1006</v>
+        <v>-3.5293</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.55</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1431</v>
+        <v>1.1572</v>
       </c>
       <c r="J292" t="n">
-        <v>25.1482</v>
+        <v>25.4584</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.47</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0354</v>
+        <v>1.042</v>
       </c>
       <c r="J293" t="n">
-        <v>22.7788</v>
+        <v>22.924</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.42</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9513</v>
       </c>
       <c r="J294" t="n">
-        <v>21.0342</v>
+        <v>20.9286</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.17</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4567</v>
+        <v>0.426</v>
       </c>
       <c r="J295" t="n">
-        <v>10.0474</v>
+        <v>9.372</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.16</v>
       </c>
       <c r="I296" t="n">
-        <v>0.4335</v>
+        <v>0.4023</v>
       </c>
       <c r="J296" t="n">
-        <v>9.537000000000001</v>
+        <v>8.8506</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.95</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0577</v>
+        <v>-0.0451</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.2694</v>
+        <v>-0.9922</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.88</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1453</v>
+        <v>-0.1299</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.1966</v>
+        <v>-2.8578</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.83</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1997</v>
+        <v>-0.1839</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.3934</v>
+        <v>-4.0458</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3678</v>
+        <v>-0.3543</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.0916</v>
+        <v>-7.7946</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.46</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5352</v>
+        <v>-0.5386</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.7744</v>
+        <v>-11.8492</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.89</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5379</v>
+        <v>1.5723</v>
       </c>
       <c r="J302" t="n">
-        <v>30.758</v>
+        <v>31.446</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.85</v>
       </c>
       <c r="I303" t="n">
-        <v>1.4907</v>
+        <v>1.5218</v>
       </c>
       <c r="J303" t="n">
-        <v>29.814</v>
+        <v>30.436</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8675</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>17.35</v>
+        <v>17.228</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.25</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6095</v>
+        <v>0.5859</v>
       </c>
       <c r="J305" t="n">
-        <v>12.19</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.18</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4567</v>
+        <v>0.426</v>
       </c>
       <c r="J306" t="n">
-        <v>9.134</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.77</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.2196</v>
+        <v>-0.2019</v>
       </c>
       <c r="J307" t="n">
-        <v>-4.392</v>
+        <v>-4.038</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.76</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2304</v>
+        <v>-0.2137</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.608</v>
+        <v>-4.274</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.423</v>
+        <v>-0.4177</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.353999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.47</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4999</v>
+        <v>-0.4986</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.997999999999999</v>
+        <v>-9.972</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.23</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7138</v>
+        <v>-0.7462</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.276</v>
+        <v>-14.924</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.64</v>
       </c>
       <c r="I312" t="n">
-        <v>1.2541</v>
+        <v>1.2719</v>
       </c>
       <c r="J312" t="n">
-        <v>23.8279</v>
+        <v>24.1661</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.59</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1903</v>
+        <v>1.2061</v>
       </c>
       <c r="J313" t="n">
-        <v>22.6157</v>
+        <v>22.9159</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.52</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0996</v>
+        <v>1.1135</v>
       </c>
       <c r="J314" t="n">
-        <v>20.8924</v>
+        <v>21.1565</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4977</v>
+        <v>0.4683</v>
       </c>
       <c r="J315" t="n">
-        <v>9.456300000000001</v>
+        <v>8.8977</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.98</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1649</v>
+        <v>-0.141</v>
       </c>
       <c r="J316" t="n">
-        <v>-3.1331</v>
+        <v>-2.679</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.08</v>
       </c>
       <c r="I317" t="n">
-        <v>0.275</v>
+        <v>0.2343</v>
       </c>
       <c r="J317" t="n">
-        <v>5.225</v>
+        <v>4.4517</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.92</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1014</v>
+        <v>-0.0872</v>
       </c>
       <c r="J318" t="n">
-        <v>-1.9266</v>
+        <v>-1.6568</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.76</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2697</v>
+        <v>-0.2529</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.1243</v>
+        <v>-4.8051</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.61</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4062</v>
+        <v>-0.3952</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.7178</v>
+        <v>-7.5088</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.51</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4943</v>
+        <v>-0.4925</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.3917</v>
+        <v>-9.3575</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.59</v>
       </c>
       <c r="I322" t="n">
-        <v>1.2024</v>
+        <v>1.2175</v>
       </c>
       <c r="J322" t="n">
-        <v>26.4528</v>
+        <v>26.785</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.55</v>
       </c>
       <c r="I323" t="n">
-        <v>1.1499</v>
+        <v>1.1635</v>
       </c>
       <c r="J323" t="n">
-        <v>25.2978</v>
+        <v>25.597</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.23</v>
       </c>
       <c r="I324" t="n">
-        <v>0.5957</v>
+        <v>0.5678</v>
       </c>
       <c r="J324" t="n">
-        <v>13.1054</v>
+        <v>12.4916</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3925</v>
+        <v>0.3605</v>
       </c>
       <c r="J325" t="n">
-        <v>8.635</v>
+        <v>7.931</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.05</v>
       </c>
       <c r="I326" t="n">
-        <v>0.1508</v>
+        <v>0.1245</v>
       </c>
       <c r="J326" t="n">
-        <v>3.3176</v>
+        <v>2.739</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.25</v>
       </c>
       <c r="I327" t="n">
-        <v>0.609</v>
+        <v>0.57</v>
       </c>
       <c r="J327" t="n">
-        <v>13.398</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.85</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.18</v>
+        <v>-0.1642</v>
       </c>
       <c r="J328" t="n">
-        <v>-3.96</v>
+        <v>-3.6124</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.83</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2011</v>
+        <v>-0.1851</v>
       </c>
       <c r="J329" t="n">
-        <v>-4.4242</v>
+        <v>-4.0722</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.58</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4315</v>
+        <v>-0.4227</v>
       </c>
       <c r="J330" t="n">
-        <v>-9.493</v>
+        <v>-9.2994</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.31</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.664</v>
+        <v>-0.6896</v>
       </c>
       <c r="J331" t="n">
-        <v>-14.608</v>
+        <v>-15.1712</v>
       </c>
     </row>
   </sheetData>
